--- a/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
   <si>
     <t>VOYA</t>
   </si>
@@ -656,211 +656,217 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1819000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1823000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1871000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1835000</v>
       </c>
-      <c r="G8" s="3">
-        <v>1530000</v>
-      </c>
       <c r="H8" s="3">
+        <v>1538000</v>
+      </c>
+      <c r="I8" s="3">
         <v>1345000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1524000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1506000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1677000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2009000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2503000</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="O8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2231000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5505000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1719000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1705000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1844000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1878000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1972000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1848000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>837000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2259000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2114000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1981000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1281400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2185000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2192000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2059000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8822000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2541200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -871,180 +877,186 @@
         <v>57000</v>
       </c>
       <c r="F9" s="3">
+        <v>57000</v>
+      </c>
+      <c r="G9" s="3">
         <v>59000</v>
       </c>
-      <c r="G9" s="3">
-        <v>30000</v>
-      </c>
       <c r="H9" s="3">
+        <v>83000</v>
+      </c>
+      <c r="I9" s="3">
         <v>60000</v>
-      </c>
-      <c r="I9" s="3">
-        <v>62000</v>
       </c>
       <c r="J9" s="3">
         <v>62000</v>
       </c>
       <c r="K9" s="3">
+        <v>62000</v>
+      </c>
+      <c r="L9" s="3">
         <v>40000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>190000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>539000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>336000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>76000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>46000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>36000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>43000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>57000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>-27000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>86000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>74000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>100000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>-34400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>209000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>195000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>64000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>415000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1762000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1766000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1814000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1776000</v>
       </c>
-      <c r="G10" s="3">
-        <v>1500000</v>
-      </c>
       <c r="H10" s="3">
+        <v>1455000</v>
+      </c>
+      <c r="I10" s="3">
         <v>1285000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1462000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1444000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1637000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1819000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2477000</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="O10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2215000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5169000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1700000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1629000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1798000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1842000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1929000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1791000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>864000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2173000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2040000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1881000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1315800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1976000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1997000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1995000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8407000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2360500</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1089,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1169,8 +1182,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,85 +1277,88 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E14" s="3">
         <v>18000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>34000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>45000</v>
       </c>
-      <c r="G14" s="3">
-        <v>8000</v>
-      </c>
       <c r="H14" s="3">
+        <v>80000</v>
+      </c>
+      <c r="I14" s="3">
         <v>15000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>10000</v>
-      </c>
-      <c r="K14" s="3">
-        <v>3000</v>
       </c>
       <c r="L14" s="3">
         <v>3000</v>
       </c>
       <c r="M14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="N14" s="3">
         <v>13000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>1000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>80000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>50000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>20000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>31000</v>
-      </c>
-      <c r="T14" s="3">
-        <v>3000</v>
       </c>
       <c r="U14" s="3">
         <v>3000</v>
       </c>
       <c r="V14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="W14" s="3">
         <v>26000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>6000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>7000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>14000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>15800</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>1000</v>
       </c>
       <c r="AC14" s="3">
         <v>1000</v>
@@ -1348,13 +1367,16 @@
         <v>1000</v>
       </c>
       <c r="AE14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF14" s="3">
         <v>34000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1445,8 +1467,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1476,192 +1501,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1637000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1575000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1514000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1646000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1399000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1407000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1231000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1326000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1338000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1308000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1548000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1424000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-3049000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1682000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5510000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1711000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1618000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1716000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1670000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1671000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1699000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>667000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2018000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1811000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1905000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1000900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2078000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1965000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1883000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8422000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E18" s="3">
         <v>248000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>357000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>189000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>131000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>114000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>198000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>168000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>369000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>461000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1079000</v>
       </c>
-      <c r="N18" s="3" t="s">
+      <c r="O18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>549000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>87000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>128000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>208000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>301000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>149000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>170000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>241000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>303000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>76000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>280500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>107000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>227000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>176000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>400000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-283800</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1694,8 +1726,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1729,12 +1762,12 @@
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1786,34 +1819,37 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>183000</v>
+      </c>
+      <c r="E21" s="3">
         <v>247000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>359000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>209000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>130000</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="3">
         <v>179000</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>8</v>
@@ -1824,14 +1860,14 @@
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>549000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5000</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>8</v>
@@ -1878,284 +1914,296 @@
       <c r="AF21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E22" s="3">
         <v>76000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>94000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>48000</v>
       </c>
       <c r="G22" s="3">
         <v>48000</v>
       </c>
       <c r="H22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="I22" s="3">
         <v>43000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>46000</v>
       </c>
       <c r="J22" s="3">
         <v>46000</v>
       </c>
       <c r="K22" s="3">
+        <v>46000</v>
+      </c>
+      <c r="L22" s="3">
         <v>69000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>50000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>51000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>54000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>48000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>138000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>50000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>43000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>48000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>59000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>58000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>47000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>90000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>55000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>62000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>55000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>62300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>67000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>72000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>63000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>390000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>72100</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E23" s="3">
         <v>172000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>263000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>141000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>83000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>71000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>152000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>122000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>300000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>411000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1028000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1038000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>501000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-143000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-42000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>44000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>80000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>149000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>243000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>102000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>80000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>186000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>241000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>21000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>218200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>40000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>155000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>113000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>10000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-355900</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-74000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>28000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-54000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>29000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-202000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>40000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>112000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-48000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>55000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-72000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-6000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-264000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>33000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>9000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-41000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>21000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>45000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>42000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>93000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-29000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-119400</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2246,192 +2294,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E26" s="3">
         <v>246000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>235000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>129000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>137000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>42000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>143000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>111000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>502000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>371000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>916000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1086000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>446000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-71000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-48000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>50000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>344000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>144000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>210000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>93000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>121000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>165000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>196000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>17000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>176200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>80000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>155000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>20000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>39000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-236500</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E27" s="3">
         <v>248000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>154000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>69000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>190000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>166000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>64000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>54000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>398000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>143000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>465000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1072000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>318000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-136000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>27000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>30000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>334000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>111000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>184000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>84000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>57000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>142000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>138000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>17000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>94700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>15000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>103000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>19000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>10000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2522,13 +2579,16 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>8</v>
@@ -2536,8 +2596,8 @@
       <c r="F29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
@@ -2549,73 +2609,76 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>5000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-1000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-6000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>14000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-58000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-363000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-93000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-128000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-1119000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-4000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>42000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-20000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>64000</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>28000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>429000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-3259000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>134000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>64000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-162000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-337000</v>
       </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2706,8 +2769,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2798,8 +2864,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2833,12 +2902,12 @@
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2890,100 +2959,106 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E33" s="3">
         <v>248000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>154000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>69000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>190000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>166000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>64000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>54000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>403000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>142000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>459000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1086000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>260000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-499000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-66000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-98000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-785000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>107000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>226000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>64000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>121000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>142000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>166000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>446000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>149000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>167000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-143000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-327000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3074,197 +3149,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E35" s="3">
         <v>248000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>154000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>69000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>190000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>166000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>64000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>54000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>403000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>142000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>459000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1086000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>260000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-499000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-66000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-98000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-785000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>107000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>226000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>64000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>121000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>142000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>166000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>446000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>149000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>167000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-143000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-327000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3297,8 +3381,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3331,100 +3416,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1118000</v>
+      </c>
+      <c r="E41" s="3">
         <v>917000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1349000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>824000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1007000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>935000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1039000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1125000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1573000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1818000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1850000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1316000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1723000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1136000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1149000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1085000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1249000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1450000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1541000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1340000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1568000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1885000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1620000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1597000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1435000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2072900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2713300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2531300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2229000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2951600</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3515,40 +3604,43 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11982000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11765000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12131000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12438000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12426000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>13561000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13079000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13261000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13635000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13580000</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>8</v>
@@ -3562,8 +3654,8 @@
       <c r="Q43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="R43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -3607,8 +3699,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3699,8 +3794,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3791,8 +3889,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3883,100 +3984,106 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>35683000</v>
+      </c>
+      <c r="E47" s="3">
         <v>34886000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>36406000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>37813000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>38086000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>38408000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>39911000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>41978000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>44387000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>47491000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>45341000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>44660000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>54841000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>54357000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>54264000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>51772000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>52700000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>67153000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>65417000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>64204000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>49918000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>62277000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>62241000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>63014000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>64644000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>93681000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>90575600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>89116700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>61153000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>93051100</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4043,17 +4150,17 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>8</v>
+      <c r="Y48" s="3">
+        <v>0</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB48" s="3">
         <v>107000</v>
-      </c>
-      <c r="AB48" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>8</v>
@@ -4061,34 +4168,37 @@
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF48" s="3">
         <v>112300</v>
       </c>
-      <c r="AF48" s="3" t="s">
+      <c r="AG48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1605000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1648000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1554000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1551000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>958000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>824000</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>8</v>
@@ -4105,8 +4215,8 @@
       <c r="N49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -4135,32 +4245,35 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>8</v>
+      <c r="Y49" s="3">
+        <v>0</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB49" s="3">
         <v>186000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>196000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>197800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>208000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>219500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>227300</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4251,8 +4364,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4343,100 +4459,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2160000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2438000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2161000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2122000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2223000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1931000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1795000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1405000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>986000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>691000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>690000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>935000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>21889000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>21494000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>21249000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>20902000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>22953000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>401000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>576000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>864000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>21655000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1122000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1266000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>58102000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>59833000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1663700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1756900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2055700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>66368800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1128100</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4527,100 +4649,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>157085000</v>
+      </c>
+      <c r="E54" s="3">
         <v>149265000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>154616000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>151208000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>146606000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>144048000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>147520000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>161806000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>171262000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>168417000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>168194000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>162861000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>180518000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>171466000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>166934000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>155732000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>168990000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>166850000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>165162000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>161985000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>155430000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>165036000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>162740000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>219824000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>222532000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>226643900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>219838800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>217025500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>214585000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>218622200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4653,8 +4781,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4687,8 +4816,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4779,28 +4909,31 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>143000</v>
       </c>
       <c r="F58" s="3">
         <v>143000</v>
       </c>
       <c r="G58" s="3">
-        <v>141000</v>
+        <v>143000</v>
       </c>
       <c r="H58" s="3">
         <v>141000</v>
       </c>
       <c r="I58" s="3">
-        <v>1000</v>
+        <v>141000</v>
       </c>
       <c r="J58" s="3">
         <v>1000</v>
@@ -4836,10 +4969,10 @@
         <v>1000</v>
       </c>
       <c r="U58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V58" s="3">
         <v>97000</v>
-      </c>
-      <c r="V58" s="3">
-        <v>1000</v>
       </c>
       <c r="W58" s="3">
         <v>1000</v>
@@ -4851,120 +4984,126 @@
         <v>1000</v>
       </c>
       <c r="Z58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>337000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>336600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>735900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>735500</v>
-      </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>94254000</v>
+      </c>
+      <c r="E59" s="3">
         <v>86681000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>90152000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>85897000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>81476000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>77358000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>81237000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>94232000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>101616000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>97995000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>98102000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>93872000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>90905000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>83454000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>80129000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>71002000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>83043000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>82049000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>81887000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>79627000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>71297000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>83034000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>80599000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>79668000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>79471000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>111603200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>105725300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>103261300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>67883100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>101627000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5055,19 +5194,22 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2095000</v>
+        <v>2097000</v>
       </c>
       <c r="E61" s="3">
         <v>2095000</v>
       </c>
       <c r="F61" s="3">
-        <v>2094000</v>
+        <v>2095000</v>
       </c>
       <c r="G61" s="3">
         <v>2094000</v>
@@ -5076,79 +5218,82 @@
         <v>2094000</v>
       </c>
       <c r="I61" s="3">
+        <v>2094000</v>
+      </c>
+      <c r="J61" s="3">
         <v>2385000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2406000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2595000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2970000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>2969000</v>
       </c>
       <c r="N61" s="3">
         <v>2969000</v>
       </c>
       <c r="O61" s="3">
+        <v>2969000</v>
+      </c>
+      <c r="P61" s="3">
         <v>3044000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>3043000</v>
       </c>
       <c r="Q61" s="3">
         <v>3043000</v>
       </c>
       <c r="R61" s="3">
-        <v>3042000</v>
+        <v>3043000</v>
       </c>
       <c r="S61" s="3">
         <v>3042000</v>
       </c>
       <c r="T61" s="3">
-        <v>3041000</v>
+        <v>3042000</v>
       </c>
       <c r="U61" s="3">
         <v>3041000</v>
       </c>
       <c r="V61" s="3">
-        <v>3136000</v>
+        <v>3041000</v>
       </c>
       <c r="W61" s="3">
         <v>3136000</v>
       </c>
       <c r="X61" s="3">
+        <v>3136000</v>
+      </c>
+      <c r="Y61" s="3">
         <v>3459000</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>3458000</v>
       </c>
       <c r="Z61" s="3">
         <v>3458000</v>
       </c>
       <c r="AA61" s="3">
+        <v>3458000</v>
+      </c>
+      <c r="AB61" s="3">
         <v>3123000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3122200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2726200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2725700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3550000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3548500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5164,83 +5309,86 @@
       <c r="G62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3">
         <v>196000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>205000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>213000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>226000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>274000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>304000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>333000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>18976000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18607000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18465000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>18414000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>18966000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>409000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>445000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>465000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>18454000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>516000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>527000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>56998000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>58827000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>542200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>636800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>656000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>60250000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>631400</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5331,8 +5479,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5423,8 +5574,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5515,100 +5669,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>152892000</v>
+      </c>
+      <c r="E66" s="3">
         <v>146138000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>150919000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>147254000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>143257000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>139955000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>143004000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>155608000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>163009000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>160028000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>159832000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>154930000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>170408000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>161809000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>157386000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>148305000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>159651000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>156299000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>155098000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>152920000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>147217000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>156513000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>154280000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>210446000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>212523000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>212990900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>206486600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>204135100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>201590000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>203416200</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5641,8 +5801,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5733,8 +5894,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5825,8 +5989,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5917,8 +6084,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6009,100 +6179,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>505000</v>
+      </c>
+      <c r="E72" s="3">
         <v>302000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>40000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-118000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-201000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-994000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1201000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1269000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1310000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3238000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3394000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3857000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-4957000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5152000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-4833000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-4766000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-4718000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-11665000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-11785000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-12011000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-11732000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-11853000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-11995000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-12161000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-12719000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-9655600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-9804200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-9971400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-9742000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-9310300</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6193,8 +6369,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6285,8 +6464,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6377,100 +6559,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4193000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3127000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3697000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3954000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3349000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4093000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4516000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6198000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8253000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8389000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8362000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7931000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10110000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9657000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9548000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7427000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9339000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10551000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10064000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9065000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8213000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8523000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8460000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9378000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10009000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13653000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13352200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12890400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12995000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>15206000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6561,197 +6749,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>118000</v>
+      </c>
+      <c r="E81" s="3">
         <v>248000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>154000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>69000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>190000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>166000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>64000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>54000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>403000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>142000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>459000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1086000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>260000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-499000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-66000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-98000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-785000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>107000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>226000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>64000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>121000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>142000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>166000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>446000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>149000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>167000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-143000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-327000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6784,8 +6981,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6876,8 +7074,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6968,8 +7169,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7060,8 +7264,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7152,8 +7359,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7244,8 +7454,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7336,100 +7549,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E89" s="3">
         <v>403000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>715000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>156000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>219000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>418000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>296000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>419000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>140000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>121000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>747000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-936000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>421000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>788000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>508000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-76000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>459000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>302000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>418000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>131000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>234000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>580000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>653000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>401000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>456000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>570000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>605800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-49800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3591000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>819700</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7462,8 +7681,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7536,26 +7756,29 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-9700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-10400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-66700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-25800</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7646,8 +7869,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7738,100 +7964,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>833000</v>
+      </c>
+      <c r="E94" s="3">
         <v>430000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>797000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>472000</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-372000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-403000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-578000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-600000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>181000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>670000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-636000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1825000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-139000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-811000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-374000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-954000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>117000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-44000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-333000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-36000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-149000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>236000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-145000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1581300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-892500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>190800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3683000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1924000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7864,8 +8096,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7873,91 +8106,94 @@
         <v>-42000</v>
       </c>
       <c r="E96" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="F96" s="3">
         <v>-23000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-20000</v>
       </c>
       <c r="G96" s="3">
         <v>-20000</v>
       </c>
       <c r="H96" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="I96" s="3">
         <v>-22000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-20000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-21000</v>
       </c>
       <c r="K96" s="3">
         <v>-21000</v>
       </c>
       <c r="L96" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="M96" s="3">
         <v>-19000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-20000</v>
       </c>
       <c r="N96" s="3">
         <v>-20000</v>
       </c>
       <c r="O96" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-18000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-58000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-19000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-20000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-21000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-20000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-1000</v>
       </c>
       <c r="W96" s="3">
         <v>-1000</v>
       </c>
       <c r="X96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1700</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-1900</v>
       </c>
       <c r="AD96" s="3">
         <v>-1900</v>
       </c>
       <c r="AE96" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8048,8 +8284,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8140,8 +8379,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8232,100 +8474,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-996000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1265000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-987000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-811000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-147000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-150000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>732000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-407000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-55000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>391000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-333000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-268000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>588000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1114000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-158000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>727000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>11000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>546000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-86000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-592000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-152000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-289000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-926000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-397000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-562400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>414200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>556600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-753400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>495400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>71300</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8416,96 +8664,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>201000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-432000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>525000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-183000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>72000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-104000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-143000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-391000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-493000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-88000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>595000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-534000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>373000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>77000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>211000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-160000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>96000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-106000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>449000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-505000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-251000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>255000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-422000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>240000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-251200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-600500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>269100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-612400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>398000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1033000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
   <si>
     <t>VOYA</t>
   </si>
@@ -656,222 +656,228 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2051000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1819000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1823000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1871000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1835000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1538000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1345000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1524000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1506000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1677000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2009000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2503000</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="3">
         <v>2231000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5505000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1719000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1705000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1844000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1878000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1972000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1848000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>837000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2259000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2114000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1981000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1281400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2185000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2192000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2059000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8822000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2541200</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>57000</v>
+        <v>56000</v>
       </c>
       <c r="E9" s="3">
         <v>57000</v>
@@ -880,183 +886,189 @@
         <v>57000</v>
       </c>
       <c r="G9" s="3">
+        <v>57000</v>
+      </c>
+      <c r="H9" s="3">
         <v>59000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>83000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>60000</v>
-      </c>
-      <c r="J9" s="3">
-        <v>62000</v>
       </c>
       <c r="K9" s="3">
         <v>62000</v>
       </c>
       <c r="L9" s="3">
+        <v>62000</v>
+      </c>
+      <c r="M9" s="3">
         <v>40000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>190000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>539000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>336000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>76000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>46000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>36000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>43000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>57000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>-27000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>86000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>74000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>100000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>-34400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>209000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>195000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>64000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>415000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1995000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1762000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1766000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1814000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1776000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1455000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1285000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1462000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1444000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1637000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1819000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2477000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="3">
         <v>2215000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5169000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1700000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1629000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1798000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1842000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1929000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1791000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>864000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2173000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2040000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1881000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1315800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1976000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1997000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1995000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8407000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2360500</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1090,8 +1102,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1185,8 +1198,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1280,88 +1296,91 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>22000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>18000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>34000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>45000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>80000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>15000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>10000</v>
-      </c>
-      <c r="L14" s="3">
-        <v>3000</v>
       </c>
       <c r="M14" s="3">
         <v>3000</v>
       </c>
       <c r="N14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="O14" s="3">
         <v>13000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>80000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>50000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>20000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>31000</v>
-      </c>
-      <c r="U14" s="3">
-        <v>3000</v>
       </c>
       <c r="V14" s="3">
         <v>3000</v>
       </c>
       <c r="W14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="X14" s="3">
         <v>26000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>6000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>7000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>14000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>15800</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>1000</v>
       </c>
       <c r="AD14" s="3">
         <v>1000</v>
@@ -1370,13 +1389,16 @@
         <v>1000</v>
       </c>
       <c r="AF14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG14" s="3">
         <v>34000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1470,8 +1492,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1502,198 +1527,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1707000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1637000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1575000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1514000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1646000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1407000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1231000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1326000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1338000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1308000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1548000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1424000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-3049000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1682000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5510000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1711000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1618000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1716000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1670000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1671000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1699000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>667000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2018000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1811000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1905000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1000900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2078000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1965000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1883000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8422000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>344000</v>
+      </c>
+      <c r="E18" s="3">
         <v>182000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>248000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>357000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>189000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>131000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>114000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>198000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>168000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>369000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>461000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1079000</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="3">
         <v>549000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>87000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>128000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>208000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>301000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>149000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>170000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>241000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>303000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>76000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>280500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>107000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>227000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>176000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>400000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-283800</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1727,8 +1759,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1765,11 +1798,11 @@
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1822,38 +1855,41 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>367000</v>
+      </c>
+      <c r="E21" s="3">
         <v>183000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>247000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>359000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>209000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>130000</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3">
         <v>179000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1863,15 +1899,15 @@
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3">
         <v>549000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1917,293 +1953,305 @@
       <c r="AG21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E22" s="3">
         <v>80000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>76000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>94000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>48000</v>
       </c>
       <c r="H22" s="3">
         <v>48000</v>
       </c>
       <c r="I22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="J22" s="3">
         <v>43000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>46000</v>
       </c>
       <c r="K22" s="3">
         <v>46000</v>
       </c>
       <c r="L22" s="3">
+        <v>46000</v>
+      </c>
+      <c r="M22" s="3">
         <v>69000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>50000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>51000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>54000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>48000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>138000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>50000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>43000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>48000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>59000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>58000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>47000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>90000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>55000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>62000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>55000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>62300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>67000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>72000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>63000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>390000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>72100</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>287000</v>
+      </c>
+      <c r="E23" s="3">
         <v>102000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>172000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>263000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>141000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>83000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>71000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>152000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>122000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>300000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>411000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1028000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1038000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>501000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-143000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-42000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>44000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>80000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>149000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>243000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>102000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>80000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>186000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>241000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>21000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>218200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>40000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>155000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>113000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>10000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-355900</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-17000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-74000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>28000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-54000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>29000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-202000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>40000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>112000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-48000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>55000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-72000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-6000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-264000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>33000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>9000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-41000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>21000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>45000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>42000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>93000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-29000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-119400</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2297,198 +2345,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>288000</v>
+      </c>
+      <c r="E26" s="3">
         <v>119000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>246000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>235000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>129000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>137000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>42000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>143000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>111000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>502000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>371000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>916000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1086000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>446000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-71000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-48000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>50000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>344000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>144000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>210000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>93000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>121000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>165000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>196000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>17000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>176200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>80000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>155000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>20000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>39000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-236500</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>234000</v>
+      </c>
+      <c r="E27" s="3">
         <v>118000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>248000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>154000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>69000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>190000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>166000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>64000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>54000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>398000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>143000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>465000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1072000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>318000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-136000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>27000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>30000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>334000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>111000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>184000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>84000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>57000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>142000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>138000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>17000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>94700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>15000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>103000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>19000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>10000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2582,16 +2639,19 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>8</v>
@@ -2599,8 +2659,8 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -2612,73 +2672,76 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>5000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-1000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-6000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>14000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-58000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-363000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-93000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-128000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-1119000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-4000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>42000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-20000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>64000</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>28000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>429000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-3259000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>134000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>64000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-162000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-337000</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2772,8 +2835,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2867,8 +2933,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2905,11 +2974,11 @@
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2962,103 +3031,109 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>234000</v>
+      </c>
+      <c r="E33" s="3">
         <v>118000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>248000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>154000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>69000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>190000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>166000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>64000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>54000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>403000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>142000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>459000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1086000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>260000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-499000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-66000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-98000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-785000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>107000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>226000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>64000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>121000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>142000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>166000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>446000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>149000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>167000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-143000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-327000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3152,203 +3227,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>234000</v>
+      </c>
+      <c r="E35" s="3">
         <v>118000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>248000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>154000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>69000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>190000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>166000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>64000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>54000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>403000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>142000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>459000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1086000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>260000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-499000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-66000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-98000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-785000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>107000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>226000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>64000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>121000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>142000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>166000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>446000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>149000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>167000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-143000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-327000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3382,8 +3466,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3417,103 +3502,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1176000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1118000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>917000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1349000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>824000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1007000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>935000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1039000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1125000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1573000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1818000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1850000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1316000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1723000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1136000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1149000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1085000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1249000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1450000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1541000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1340000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1568000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1885000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1620000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1597000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1435000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2072900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2713300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2531300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2229000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2951600</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3607,44 +3696,47 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11828000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11982000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11765000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12131000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12438000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12426000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13561000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13079000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13261000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13635000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13580000</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3657,8 +3749,8 @@
       <c r="R43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -3702,8 +3794,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3797,8 +3892,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3892,8 +3990,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3987,103 +4088,109 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>34615000</v>
+      </c>
+      <c r="E47" s="3">
         <v>35683000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>34886000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>36406000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>37813000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>38086000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>38408000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>39911000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>41978000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>44387000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>47491000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>45341000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>44660000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>54841000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>54357000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>54264000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>51772000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>52700000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>67153000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>65417000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>64204000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>49918000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>62277000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>62241000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>63014000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>64644000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>93681000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>90575600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>89116700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>61153000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>93051100</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4153,56 +4260,59 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>8</v>
+      <c r="Z48" s="3">
+        <v>0</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC48" s="3">
         <v>107000</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG48" s="3">
         <v>112300</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1609000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1605000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1648000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1554000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1551000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>958000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>824000</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4218,8 +4328,8 @@
       <c r="O49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -4248,32 +4358,35 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>8</v>
+      <c r="Z49" s="3">
+        <v>0</v>
       </c>
       <c r="AA49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AB49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC49" s="3">
         <v>186000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>196000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>197800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>208000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>219500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>227300</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4367,8 +4480,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4462,103 +4578,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2178000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2160000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2438000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2161000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2122000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2223000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1931000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1795000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1405000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>986000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>691000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>690000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>935000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>21889000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>21494000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>21249000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>20902000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>22953000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>401000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>576000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>864000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>21655000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1122000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>58102000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>59833000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1663700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1756900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2055700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>66368800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1128100</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4652,103 +4774,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>161631000</v>
+      </c>
+      <c r="E54" s="3">
         <v>157085000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>149265000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>154616000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>151208000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>146606000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>144048000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>147520000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>161806000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>171262000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>168417000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>168194000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>162861000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>180518000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>171466000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>166934000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>155732000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>168990000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>166850000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>165162000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>161985000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>155430000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>165036000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>162740000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>219824000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>222532000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>226643900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>219838800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>217025500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>214585000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>218622200</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4782,8 +4910,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4817,8 +4946,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4912,31 +5042,34 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>393000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>143000</v>
       </c>
       <c r="G58" s="3">
         <v>143000</v>
       </c>
       <c r="H58" s="3">
-        <v>141000</v>
+        <v>143000</v>
       </c>
       <c r="I58" s="3">
         <v>141000</v>
       </c>
       <c r="J58" s="3">
-        <v>1000</v>
+        <v>141000</v>
       </c>
       <c r="K58" s="3">
         <v>1000</v>
@@ -4972,10 +5105,10 @@
         <v>1000</v>
       </c>
       <c r="V58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W58" s="3">
         <v>97000</v>
-      </c>
-      <c r="W58" s="3">
-        <v>1000</v>
       </c>
       <c r="X58" s="3">
         <v>1000</v>
@@ -4987,123 +5120,129 @@
         <v>1000</v>
       </c>
       <c r="AA58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
         <v>337000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>336600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>735900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>735500</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>99856000</v>
+      </c>
+      <c r="E59" s="3">
         <v>94254000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>86681000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>90152000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>85897000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>81476000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>77358000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>81237000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>94232000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>101616000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>97995000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>98102000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>93872000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>90905000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>83454000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>80129000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>71002000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>83043000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>82049000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>81887000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>79627000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>71297000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>83034000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>80599000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>79668000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>79471000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>111603200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>105725300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>103261300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>67883100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>101627000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5197,22 +5336,25 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1707000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2097000</v>
-      </c>
-      <c r="E61" s="3">
-        <v>2095000</v>
       </c>
       <c r="F61" s="3">
         <v>2095000</v>
       </c>
       <c r="G61" s="3">
-        <v>2094000</v>
+        <v>2095000</v>
       </c>
       <c r="H61" s="3">
         <v>2094000</v>
@@ -5221,79 +5363,82 @@
         <v>2094000</v>
       </c>
       <c r="J61" s="3">
+        <v>2094000</v>
+      </c>
+      <c r="K61" s="3">
         <v>2385000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2406000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2595000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2970000</v>
-      </c>
-      <c r="N61" s="3">
-        <v>2969000</v>
       </c>
       <c r="O61" s="3">
         <v>2969000</v>
       </c>
       <c r="P61" s="3">
+        <v>2969000</v>
+      </c>
+      <c r="Q61" s="3">
         <v>3044000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>3043000</v>
       </c>
       <c r="R61" s="3">
         <v>3043000</v>
       </c>
       <c r="S61" s="3">
-        <v>3042000</v>
+        <v>3043000</v>
       </c>
       <c r="T61" s="3">
         <v>3042000</v>
       </c>
       <c r="U61" s="3">
-        <v>3041000</v>
+        <v>3042000</v>
       </c>
       <c r="V61" s="3">
         <v>3041000</v>
       </c>
       <c r="W61" s="3">
-        <v>3136000</v>
+        <v>3041000</v>
       </c>
       <c r="X61" s="3">
         <v>3136000</v>
       </c>
       <c r="Y61" s="3">
+        <v>3136000</v>
+      </c>
+      <c r="Z61" s="3">
         <v>3459000</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>3458000</v>
       </c>
       <c r="AA61" s="3">
         <v>3458000</v>
       </c>
       <c r="AB61" s="3">
+        <v>3458000</v>
+      </c>
+      <c r="AC61" s="3">
         <v>3123000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3122200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2726200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2725700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3550000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3548500</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5312,83 +5457,86 @@
       <c r="H62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3">
         <v>196000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>205000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>213000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>226000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>274000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>304000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>333000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18976000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18607000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>18465000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>18414000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>18966000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>409000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>445000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>465000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>18454000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>516000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>527000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>56998000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>58827000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>542200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>636800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>656000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>60250000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>631400</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5482,8 +5630,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5577,8 +5728,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5672,103 +5826,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>157478000</v>
+      </c>
+      <c r="E66" s="3">
         <v>152892000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>146138000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>150919000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>147254000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>143257000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>139955000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>143004000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>155608000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>163009000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>160028000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>159832000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>154930000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>170408000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>161809000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>157386000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>148305000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>159651000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>156299000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>155098000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>152920000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>147217000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>156513000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>154280000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>210446000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>212523000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>212990900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>206486600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>204135100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>201590000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>203416200</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5802,8 +5962,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5897,8 +6058,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5992,8 +6156,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6087,8 +6254,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6182,103 +6352,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>697000</v>
+      </c>
+      <c r="E72" s="3">
         <v>505000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>302000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>40000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-118000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-201000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-994000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1201000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1269000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1310000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3238000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3394000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3857000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-4957000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5152000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-4833000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-4766000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-4718000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-11665000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-11785000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-12011000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-11732000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-11853000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-11995000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-12161000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-12719000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-9655600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-9804200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-9971400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-9742000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-9310300</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6372,8 +6548,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6467,8 +6646,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6562,103 +6744,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4153000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4193000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3127000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3697000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3954000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3349000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4093000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4516000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6198000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8253000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8389000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8362000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7931000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10110000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9657000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9548000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7427000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9339000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10551000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10064000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9065000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8213000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8523000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8460000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9378000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10009000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13653000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13352200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12890400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12995000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>15206000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6752,203 +6940,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>234000</v>
+      </c>
+      <c r="E81" s="3">
         <v>118000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>248000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>154000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>69000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>190000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>166000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>64000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>54000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>403000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>142000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>459000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1086000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>260000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-499000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-66000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-98000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-785000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>107000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>226000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>64000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>121000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>142000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>166000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>446000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>149000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>167000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-143000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-327000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6982,8 +7179,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7077,8 +7275,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7172,8 +7373,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7267,8 +7471,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7362,8 +7569,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7457,8 +7667,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7552,103 +7765,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>231000</v>
+      </c>
+      <c r="E89" s="3">
         <v>364000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>403000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>715000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>156000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>219000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>418000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>296000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>419000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>140000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>121000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>747000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-936000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>421000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>788000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>508000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-76000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>459000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>302000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>418000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>131000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>234000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>580000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>653000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>401000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>456000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>570000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>605800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-49800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3591000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>819700</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7682,8 +7901,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7759,26 +7979,29 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-9700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-10400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-66700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-25800</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7872,8 +8095,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7967,103 +8193,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1082000</v>
+      </c>
+      <c r="E94" s="3">
         <v>833000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>430000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>797000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>472000</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-372000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-403000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-578000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-600000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>181000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>670000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-636000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1825000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-139000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-811000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-374000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-954000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>117000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-44000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-333000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-36000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-149000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>236000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-145000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1581300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-892500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>190800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3683000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1924000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8097,103 +8329,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-42000</v>
+        <v>-41000</v>
       </c>
       <c r="E96" s="3">
         <v>-42000</v>
       </c>
       <c r="F96" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="G96" s="3">
         <v>-23000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-20000</v>
       </c>
       <c r="H96" s="3">
         <v>-20000</v>
       </c>
       <c r="I96" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="J96" s="3">
         <v>-22000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-20000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-21000</v>
       </c>
       <c r="L96" s="3">
         <v>-21000</v>
       </c>
       <c r="M96" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="N96" s="3">
         <v>-19000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-20000</v>
       </c>
       <c r="O96" s="3">
         <v>-20000</v>
       </c>
       <c r="P96" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-58000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-19000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-20000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-21000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-20000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-1000</v>
       </c>
       <c r="X96" s="3">
         <v>-1000</v>
       </c>
       <c r="Y96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1700</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-1900</v>
       </c>
       <c r="AE96" s="3">
         <v>-1900</v>
       </c>
       <c r="AF96" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8287,8 +8523,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8382,8 +8621,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8477,103 +8719,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1255000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-996000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1265000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-987000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-811000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-147000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-150000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>732000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-407000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-55000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>391000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-333000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-268000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>588000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1114000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-158000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>727000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>11000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>546000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-86000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-592000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-152000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-289000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-926000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-397000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-562400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>414200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>556600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-753400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>495400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>71300</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8667,99 +8915,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E102" s="3">
         <v>201000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-432000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>525000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-183000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>72000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-104000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-143000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-391000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-493000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-88000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>595000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-534000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>373000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>77000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>211000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-160000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>96000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-106000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>449000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-505000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-251000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>255000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-422000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>240000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-251200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-600500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>269100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-612400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>398000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1033000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
   <si>
     <t>VOYA</t>
   </si>
@@ -656,223 +656,229 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2033000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2051000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1819000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1823000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1871000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1835000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1538000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1345000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1524000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1506000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1677000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2009000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2503000</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3">
         <v>2231000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5505000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1719000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1705000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1844000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1878000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1972000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1848000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>837000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2259000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2114000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1981000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1281400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2185000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2192000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2059000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8822000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2541200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -880,7 +886,7 @@
         <v>56000</v>
       </c>
       <c r="E9" s="3">
-        <v>57000</v>
+        <v>56000</v>
       </c>
       <c r="F9" s="3">
         <v>57000</v>
@@ -889,186 +895,192 @@
         <v>57000</v>
       </c>
       <c r="H9" s="3">
+        <v>57000</v>
+      </c>
+      <c r="I9" s="3">
         <v>59000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>83000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>60000</v>
-      </c>
-      <c r="K9" s="3">
-        <v>62000</v>
       </c>
       <c r="L9" s="3">
         <v>62000</v>
       </c>
       <c r="M9" s="3">
+        <v>62000</v>
+      </c>
+      <c r="N9" s="3">
         <v>40000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>190000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>26000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>539000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>336000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>19000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>76000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>46000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>36000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>43000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>57000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>-27000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>86000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>74000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>100000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>-34400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>209000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>195000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>64000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>415000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1977000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1995000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1762000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1766000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1814000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1776000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1455000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1285000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1462000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1444000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1637000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1819000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2477000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3">
         <v>2215000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5169000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1700000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1629000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1798000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1842000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1929000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1791000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>864000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2173000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2040000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1881000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1315800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1976000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1997000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1995000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8407000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2360500</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1103,8 +1115,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1201,8 +1214,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,91 +1315,94 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>22000</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
+        <v>55000</v>
+      </c>
+      <c r="G14" s="3">
         <v>18000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>34000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>45000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>80000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>15000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>10000</v>
-      </c>
-      <c r="M14" s="3">
-        <v>3000</v>
       </c>
       <c r="N14" s="3">
         <v>3000</v>
       </c>
       <c r="O14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P14" s="3">
         <v>13000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>1000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>80000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>50000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>20000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>31000</v>
-      </c>
-      <c r="V14" s="3">
-        <v>3000</v>
       </c>
       <c r="W14" s="3">
         <v>3000</v>
       </c>
       <c r="X14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Y14" s="3">
         <v>26000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>6000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>7000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>14000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>15800</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>1000</v>
       </c>
       <c r="AE14" s="3">
         <v>1000</v>
@@ -1392,13 +1411,16 @@
         <v>1000</v>
       </c>
       <c r="AG14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH14" s="3">
         <v>34000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1495,8 +1517,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1528,204 +1553,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1659000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1707000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1637000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1575000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1514000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1646000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1407000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1231000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1326000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1338000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1308000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1548000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1424000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-3049000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1682000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5510000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1711000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1618000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1716000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1670000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1671000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1699000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>667000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2018000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1811000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1905000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1000900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2078000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1965000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1883000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8422000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E18" s="3">
         <v>344000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>182000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>248000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>357000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>189000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>131000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>114000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>198000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>168000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>369000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>461000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1079000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3">
         <v>549000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>87000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>128000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>208000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>301000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>149000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>170000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>241000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>303000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>76000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>280500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>107000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>227000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>176000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>400000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-283800</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1760,8 +1792,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1801,11 +1834,11 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1858,41 +1891,44 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>374000</v>
+      </c>
+      <c r="E21" s="3">
         <v>367000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>183000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>247000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>359000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>209000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>130000</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="3">
         <v>179000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1902,15 +1938,15 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>549000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1956,302 +1992,314 @@
       <c r="AH21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E22" s="3">
         <v>57000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>80000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>76000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>94000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>48000</v>
       </c>
       <c r="I22" s="3">
         <v>48000</v>
       </c>
       <c r="J22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="K22" s="3">
         <v>43000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>46000</v>
       </c>
       <c r="L22" s="3">
         <v>46000</v>
       </c>
       <c r="M22" s="3">
+        <v>46000</v>
+      </c>
+      <c r="N22" s="3">
         <v>69000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>50000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>51000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>54000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>48000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>138000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>50000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>43000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>48000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>59000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>58000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>47000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>90000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>55000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>62000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>55000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>62300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>67000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>72000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>63000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>390000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>72100</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>276000</v>
+      </c>
+      <c r="E23" s="3">
         <v>287000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>102000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>172000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>263000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>141000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>83000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>71000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>152000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>122000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>300000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>411000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1028000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1038000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>501000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-143000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-42000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>44000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>80000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>149000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>243000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>102000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>80000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>186000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>241000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>21000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>218200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>40000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>155000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>113000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>10000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-355900</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-17000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-74000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>28000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>12000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-54000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>29000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-202000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>40000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>112000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-48000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>55000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-72000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-6000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-264000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>33000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>9000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-41000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>21000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>45000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>42000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>93000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-29000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-119400</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2348,204 +2396,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>235000</v>
+      </c>
+      <c r="E26" s="3">
         <v>288000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>119000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>246000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>235000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>129000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>137000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>42000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>143000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>111000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>502000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>371000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>916000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1086000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>446000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-71000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-48000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>50000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>344000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>144000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>210000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>93000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>121000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>165000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>196000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>17000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>176200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>80000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>155000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>20000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>39000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-236500</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>201000</v>
+      </c>
+      <c r="E27" s="3">
         <v>234000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>118000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>248000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>154000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>69000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>190000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>166000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>64000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>54000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>398000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>143000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>465000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1072000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>318000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-136000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>27000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>30000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>334000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>111000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>184000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>84000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>57000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>142000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>138000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>17000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>94700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>15000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>103000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>19000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>10000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2642,19 +2699,22 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>8</v>
@@ -2662,8 +2722,8 @@
       <c r="H29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2675,73 +2735,76 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>5000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-1000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-6000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>14000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-58000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-363000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-93000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-128000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-1119000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-4000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>42000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>64000</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>28000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>429000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-3259000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>134000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>64000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-162000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-337000</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2838,8 +2901,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2936,8 +3002,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2977,11 +3046,11 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3034,106 +3103,112 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>201000</v>
+      </c>
+      <c r="E33" s="3">
         <v>234000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>118000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>248000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>154000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>69000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>190000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>166000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>64000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>54000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>403000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>142000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>459000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1086000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>260000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-499000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-66000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-98000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-785000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>107000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>226000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>64000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>121000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>142000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>166000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>446000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>149000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>167000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-143000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-327000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3230,209 +3305,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>201000</v>
+      </c>
+      <c r="E35" s="3">
         <v>234000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>118000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>248000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>154000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>69000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>190000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>166000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>64000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>54000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>403000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>142000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>459000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1086000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>260000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-499000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-66000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-98000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-785000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>107000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>226000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>64000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>121000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>142000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>166000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>446000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>149000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>167000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-143000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-327000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3467,8 +3551,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3503,106 +3588,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1180000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1176000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1118000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>917000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1349000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>824000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1007000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>935000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1039000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1125000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1573000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1818000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1850000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1316000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1723000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1136000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1149000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1085000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1249000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1450000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1541000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1340000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1568000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1885000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1620000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1597000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1435000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2072900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2713300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2531300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2229000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2951600</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3699,47 +3788,50 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11574000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11828000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11982000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11765000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12131000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12438000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12426000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13561000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13079000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13261000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13635000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13580000</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3752,8 +3844,8 @@
       <c r="S43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -3797,8 +3889,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3895,8 +3990,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3993,8 +4091,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4091,106 +4192,112 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>34226000</v>
+      </c>
+      <c r="E47" s="3">
         <v>34615000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>35683000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>34886000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>36406000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>37813000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>38086000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>38408000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>39911000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>41978000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>44387000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>47491000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>45341000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>44660000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>54841000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>54357000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>54264000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>51772000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>52700000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>67153000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>65417000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>64204000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>49918000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>62277000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>62241000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>63014000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>64644000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>93681000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>90575600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>89116700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>61153000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>93051100</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4263,59 +4370,62 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>8</v>
+      <c r="AA48" s="3">
+        <v>0</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD48" s="3">
         <v>107000</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH48" s="3">
         <v>112300</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1604000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1609000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1605000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1648000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1554000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1551000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>958000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>824000</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4331,8 +4441,8 @@
       <c r="P49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -4361,32 +4471,35 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>8</v>
+      <c r="AA49" s="3">
+        <v>0</v>
       </c>
       <c r="AB49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD49" s="3">
         <v>186000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>196000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>197800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>208000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>219500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>227300</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4483,8 +4596,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4581,106 +4697,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2171000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2178000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2160000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2438000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2161000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2122000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2223000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1931000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1795000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1405000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>986000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>691000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>690000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>935000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>21889000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>21494000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>21249000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>20902000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>22953000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>401000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>576000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>864000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>21655000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1122000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>58102000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>59833000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1663700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1756900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2055700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>66368800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1128100</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4777,106 +4899,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>161280000</v>
+      </c>
+      <c r="E54" s="3">
         <v>161631000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>157085000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>149265000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>154616000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>151208000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>146606000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>144048000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>147520000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>161806000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>171262000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>168417000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>168194000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>162861000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>180518000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>171466000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>166934000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>155732000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>168990000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>166850000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>165162000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>161985000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>155430000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>165036000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>162740000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>219824000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>222532000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>226643900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>219838800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>217025500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>214585000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>218622200</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4911,8 +5039,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4947,8 +5076,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5045,34 +5175,37 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>395000</v>
+      </c>
+      <c r="E58" s="3">
         <v>393000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>143000</v>
       </c>
       <c r="H58" s="3">
         <v>143000</v>
       </c>
       <c r="I58" s="3">
-        <v>141000</v>
+        <v>143000</v>
       </c>
       <c r="J58" s="3">
         <v>141000</v>
       </c>
       <c r="K58" s="3">
-        <v>1000</v>
+        <v>141000</v>
       </c>
       <c r="L58" s="3">
         <v>1000</v>
@@ -5108,10 +5241,10 @@
         <v>1000</v>
       </c>
       <c r="W58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X58" s="3">
         <v>97000</v>
-      </c>
-      <c r="X58" s="3">
-        <v>1000</v>
       </c>
       <c r="Y58" s="3">
         <v>1000</v>
@@ -5123,126 +5256,132 @@
         <v>1000</v>
       </c>
       <c r="AB58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
         <v>337000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>336600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>735900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>735500</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH58" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100362000</v>
+      </c>
+      <c r="E59" s="3">
         <v>99856000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>94254000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>86681000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>90152000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>85897000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>81476000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>77358000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>81237000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>94232000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>101616000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>97995000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>98102000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>93872000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>90905000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>83454000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>80129000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>71002000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>83043000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>82049000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>81887000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>79627000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>71297000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>83034000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>80599000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>79668000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>79471000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>111603200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>105725300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>103261300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>67883100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>101627000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5339,8 +5478,11 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5348,16 +5490,16 @@
         <v>1707000</v>
       </c>
       <c r="E61" s="3">
+        <v>1707000</v>
+      </c>
+      <c r="F61" s="3">
         <v>2097000</v>
-      </c>
-      <c r="F61" s="3">
-        <v>2095000</v>
       </c>
       <c r="G61" s="3">
         <v>2095000</v>
       </c>
       <c r="H61" s="3">
-        <v>2094000</v>
+        <v>2095000</v>
       </c>
       <c r="I61" s="3">
         <v>2094000</v>
@@ -5366,79 +5508,82 @@
         <v>2094000</v>
       </c>
       <c r="K61" s="3">
+        <v>2094000</v>
+      </c>
+      <c r="L61" s="3">
         <v>2385000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2406000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2595000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2970000</v>
-      </c>
-      <c r="O61" s="3">
-        <v>2969000</v>
       </c>
       <c r="P61" s="3">
         <v>2969000</v>
       </c>
       <c r="Q61" s="3">
+        <v>2969000</v>
+      </c>
+      <c r="R61" s="3">
         <v>3044000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>3043000</v>
       </c>
       <c r="S61" s="3">
         <v>3043000</v>
       </c>
       <c r="T61" s="3">
-        <v>3042000</v>
+        <v>3043000</v>
       </c>
       <c r="U61" s="3">
         <v>3042000</v>
       </c>
       <c r="V61" s="3">
-        <v>3041000</v>
+        <v>3042000</v>
       </c>
       <c r="W61" s="3">
         <v>3041000</v>
       </c>
       <c r="X61" s="3">
-        <v>3136000</v>
+        <v>3041000</v>
       </c>
       <c r="Y61" s="3">
         <v>3136000</v>
       </c>
       <c r="Z61" s="3">
+        <v>3136000</v>
+      </c>
+      <c r="AA61" s="3">
         <v>3459000</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>3458000</v>
       </c>
       <c r="AB61" s="3">
         <v>3458000</v>
       </c>
       <c r="AC61" s="3">
+        <v>3458000</v>
+      </c>
+      <c r="AD61" s="3">
         <v>3123000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3122200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2726200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2725700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3550000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3548500</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5460,83 +5605,86 @@
       <c r="I62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>196000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>205000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>213000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>226000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>274000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>304000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>333000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18976000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>18607000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>18465000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>18414000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>18966000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>409000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>445000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>465000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>18454000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>516000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>527000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>56998000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>58827000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>542200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>636800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>656000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>60250000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>631400</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5633,8 +5781,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5731,8 +5882,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5829,106 +5983,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>157237000</v>
+      </c>
+      <c r="E66" s="3">
         <v>157478000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>152892000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>146138000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>150919000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>147254000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>143257000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>139955000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>143004000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>155608000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>163009000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>160028000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>159832000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>154930000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>170408000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>161809000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>157386000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>148305000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>159651000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>156299000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>155098000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>152920000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>147217000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>156513000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>154280000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>210446000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>212523000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>212990900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>206486600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>204135100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>201590000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>203416200</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5963,8 +6123,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6061,8 +6222,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6159,8 +6323,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6257,8 +6424,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6355,106 +6525,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>855000</v>
+      </c>
+      <c r="E72" s="3">
         <v>697000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>505000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>302000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>40000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-118000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-201000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-994000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1201000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1269000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1310000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-3238000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3394000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3857000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-4957000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-5152000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-4833000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-4766000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-4718000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-11665000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-11785000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-12011000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-11732000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-11853000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-11995000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-12161000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-12719000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-9655600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-9804200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-9971400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-9742000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-9310300</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6551,8 +6727,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6649,8 +6828,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6747,106 +6929,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4043000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4153000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4193000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3127000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3697000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3954000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3349000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4093000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4516000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6198000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8253000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8389000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8362000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7931000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10110000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9657000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9548000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7427000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9339000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10551000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10064000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9065000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8213000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8523000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8460000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9378000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10009000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13653000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13352200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12890400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12995000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>15206000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6943,209 +7131,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>201000</v>
+      </c>
+      <c r="E81" s="3">
         <v>234000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>118000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>248000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>154000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>69000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>190000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>166000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>64000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>54000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>403000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>142000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>459000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1086000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>260000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-499000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-66000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-98000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-785000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>107000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>226000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>64000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>121000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>142000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>166000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>446000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>149000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>167000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-143000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-327000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7180,8 +7377,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7278,8 +7476,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7376,8 +7577,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7474,8 +7678,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7572,8 +7779,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7670,8 +7880,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7768,106 +7981,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>316000</v>
+      </c>
+      <c r="E89" s="3">
         <v>231000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>364000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>403000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>715000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>156000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>219000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>418000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>296000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>419000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>140000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>121000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>747000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-936000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>421000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>788000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>508000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-76000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>459000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>302000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>418000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>131000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>234000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>580000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>653000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>401000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>456000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>570000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>605800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-49800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3591000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>819700</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7902,8 +8121,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7982,26 +8202,29 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD91" s="3">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-9700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-10400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-66700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-25800</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8098,8 +8321,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8196,106 +8422,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-92000</v>
+      </c>
+      <c r="E94" s="3">
         <v>1082000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>833000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>430000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>797000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>472000</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-372000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-403000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-578000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-600000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>181000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>670000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-636000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1825000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-139000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-811000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-374000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-954000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>117000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-44000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-333000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-36000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-149000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>236000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-145000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1581300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-892500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>190800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3683000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1924000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8330,106 +8562,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-41000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-42000</v>
       </c>
       <c r="F96" s="3">
         <v>-42000</v>
       </c>
       <c r="G96" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="H96" s="3">
         <v>-23000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-20000</v>
       </c>
       <c r="I96" s="3">
         <v>-20000</v>
       </c>
       <c r="J96" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-22000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-20000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-21000</v>
       </c>
       <c r="M96" s="3">
         <v>-21000</v>
       </c>
       <c r="N96" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-19000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-20000</v>
       </c>
       <c r="P96" s="3">
         <v>-20000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-18000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-58000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-19000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-20000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-21000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-20000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-1000</v>
       </c>
       <c r="Y96" s="3">
         <v>-1000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1700</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-1900</v>
       </c>
       <c r="AF96" s="3">
         <v>-1900</v>
       </c>
       <c r="AG96" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8526,8 +8762,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8624,8 +8863,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8722,106 +8964,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-220000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1255000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-996000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1265000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-987000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-811000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-147000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-150000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>732000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-407000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-55000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>391000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-333000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-268000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>588000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1114000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-158000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>727000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>11000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>546000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-86000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-592000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-152000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-289000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-926000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-397000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-562400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>414200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>556600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-753400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>495400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>71300</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8918,102 +9166,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E102" s="3">
         <v>58000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>201000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-432000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>525000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-183000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>72000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-104000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-143000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-391000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-493000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-88000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>595000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-534000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>373000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>77000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>211000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-160000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>96000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-106000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>449000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-505000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-251000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>255000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-422000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>240000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-251200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-600500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>269100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-612400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>398000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1033000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="92">
   <si>
     <t>VOYA</t>
   </si>
@@ -656,431 +656,443 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1956000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2033000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2051000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1819000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1823000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1871000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1835000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1538000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1345000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1524000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1506000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1677000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2009000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2503000</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S8" s="3">
         <v>2231000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5505000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1719000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1705000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1844000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1878000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1972000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1848000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>837000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2259000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2114000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1981000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1281400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2185000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2192000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2059000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>8822000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2541200</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>56000</v>
+        <v>993000</v>
       </c>
       <c r="E9" s="3">
-        <v>56000</v>
+        <v>899000</v>
       </c>
       <c r="F9" s="3">
-        <v>57000</v>
+        <v>907000</v>
       </c>
       <c r="G9" s="3">
-        <v>57000</v>
+        <v>861000</v>
       </c>
       <c r="H9" s="3">
-        <v>57000</v>
+        <v>856000</v>
       </c>
       <c r="I9" s="3">
-        <v>59000</v>
+        <v>739000</v>
       </c>
       <c r="J9" s="3">
+        <v>810000</v>
+      </c>
+      <c r="K9" s="3">
         <v>83000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>60000</v>
-      </c>
-      <c r="L9" s="3">
-        <v>62000</v>
       </c>
       <c r="M9" s="3">
         <v>62000</v>
       </c>
       <c r="N9" s="3">
+        <v>62000</v>
+      </c>
+      <c r="O9" s="3">
         <v>40000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>190000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>539000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>336000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>76000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>46000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>36000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>43000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>57000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>-27000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>86000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>74000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>100000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>-34400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>209000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>195000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>64000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>415000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1977000</v>
+        <v>963000</v>
       </c>
       <c r="E10" s="3">
+        <v>1134000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1144000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>958000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>967000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1132000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1025000</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1455000</v>
+      </c>
+      <c r="L10" s="3">
+        <v>1285000</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1462000</v>
+      </c>
+      <c r="N10" s="3">
+        <v>1444000</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1637000</v>
+      </c>
+      <c r="P10" s="3">
+        <v>1819000</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>2477000</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3">
+        <v>2215000</v>
+      </c>
+      <c r="T10" s="3">
+        <v>5169000</v>
+      </c>
+      <c r="U10" s="3">
+        <v>1700000</v>
+      </c>
+      <c r="V10" s="3">
+        <v>1629000</v>
+      </c>
+      <c r="W10" s="3">
+        <v>1798000</v>
+      </c>
+      <c r="X10" s="3">
+        <v>1842000</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>1929000</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>1791000</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>864000</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>2173000</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>2040000</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>1881000</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>1315800</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>1976000</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>1997000</v>
+      </c>
+      <c r="AH10" s="3">
         <v>1995000</v>
       </c>
-      <c r="F10" s="3">
-        <v>1762000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1766000</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1814000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1776000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1455000</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1285000</v>
-      </c>
-      <c r="L10" s="3">
-        <v>1462000</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1444000</v>
-      </c>
-      <c r="N10" s="3">
-        <v>1637000</v>
-      </c>
-      <c r="O10" s="3">
-        <v>1819000</v>
-      </c>
-      <c r="P10" s="3">
-        <v>2477000</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R10" s="3">
-        <v>2215000</v>
-      </c>
-      <c r="S10" s="3">
-        <v>5169000</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1700000</v>
-      </c>
-      <c r="U10" s="3">
-        <v>1629000</v>
-      </c>
-      <c r="V10" s="3">
-        <v>1798000</v>
-      </c>
-      <c r="W10" s="3">
-        <v>1842000</v>
-      </c>
-      <c r="X10" s="3">
-        <v>1929000</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>1791000</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>864000</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>2173000</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>2040000</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>1881000</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>1315800</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>1976000</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>1997000</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>1995000</v>
-      </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8407000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2360500</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1116,8 +1128,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1217,8 +1230,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1318,8 +1334,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1329,83 +1348,83 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>55000</v>
       </c>
-      <c r="G14" s="3">
-        <v>18000</v>
-      </c>
-      <c r="H14" s="3">
-        <v>34000</v>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
-        <v>45000</v>
+        <v>12000</v>
       </c>
       <c r="J14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K14" s="3">
         <v>80000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>15000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>10000</v>
-      </c>
-      <c r="N14" s="3">
-        <v>3000</v>
       </c>
       <c r="O14" s="3">
         <v>3000</v>
       </c>
       <c r="P14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Q14" s="3">
         <v>13000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>1000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>80000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>50000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>20000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>31000</v>
-      </c>
-      <c r="W14" s="3">
-        <v>3000</v>
       </c>
       <c r="X14" s="3">
         <v>3000</v>
       </c>
       <c r="Y14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Z14" s="3">
         <v>26000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>6000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>7000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>14000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>15800</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>1000</v>
       </c>
       <c r="AF14" s="3">
         <v>1000</v>
@@ -1414,36 +1433,39 @@
         <v>1000</v>
       </c>
       <c r="AH14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AI14" s="3">
         <v>34000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>21300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>21300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1520,8 +1542,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1554,210 +1579,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1771000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1659000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1707000</v>
       </c>
-      <c r="F17" s="3">
-        <v>1637000</v>
-      </c>
       <c r="G17" s="3">
+        <v>1582000</v>
+      </c>
+      <c r="H17" s="3">
         <v>1575000</v>
       </c>
-      <c r="H17" s="3">
-        <v>1514000</v>
-      </c>
       <c r="I17" s="3">
-        <v>1646000</v>
+        <v>1502000</v>
       </c>
       <c r="J17" s="3">
+        <v>1644000</v>
+      </c>
+      <c r="K17" s="3">
         <v>1407000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1231000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1326000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1338000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1308000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1548000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1424000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-3049000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1682000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5510000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1711000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1618000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1716000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1670000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1671000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1699000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>667000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2018000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1811000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1905000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1000900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2078000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1965000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1883000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8422000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>185000</v>
+      </c>
+      <c r="E18" s="3">
         <v>374000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>344000</v>
       </c>
-      <c r="F18" s="3">
-        <v>182000</v>
-      </c>
       <c r="G18" s="3">
+        <v>237000</v>
+      </c>
+      <c r="H18" s="3">
         <v>248000</v>
       </c>
-      <c r="H18" s="3">
-        <v>357000</v>
-      </c>
       <c r="I18" s="3">
-        <v>189000</v>
+        <v>369000</v>
       </c>
       <c r="J18" s="3">
+        <v>191000</v>
+      </c>
+      <c r="K18" s="3">
         <v>131000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>114000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>198000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>168000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>369000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>461000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1079000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="3">
         <v>549000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>87000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>128000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>208000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>301000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>149000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>170000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>241000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>303000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>76000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>280500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>107000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>227000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>176000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>400000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-283800</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1793,31 +1825,32 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1837,11 +1870,11 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
@@ -1894,44 +1927,47 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>374000</v>
+        <v>209000</v>
       </c>
       <c r="E21" s="3">
-        <v>367000</v>
+        <v>397000</v>
       </c>
       <c r="F21" s="3">
-        <v>183000</v>
+        <v>365300</v>
       </c>
       <c r="G21" s="3">
-        <v>247000</v>
+        <v>258300</v>
       </c>
       <c r="H21" s="3">
-        <v>359000</v>
+        <v>269000</v>
       </c>
       <c r="I21" s="3">
-        <v>209000</v>
+        <v>390000</v>
       </c>
       <c r="J21" s="3">
+        <v>200000</v>
+      </c>
+      <c r="K21" s="3">
         <v>130000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>179000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1941,15 +1977,15 @@
       <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3">
         <v>549000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1995,311 +2031,323 @@
       <c r="AI21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E22" s="3">
         <v>98000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>57000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>80000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>76000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>94000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>48000</v>
       </c>
       <c r="J22" s="3">
         <v>48000</v>
       </c>
       <c r="K22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="L22" s="3">
         <v>43000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>46000</v>
       </c>
       <c r="M22" s="3">
         <v>46000</v>
       </c>
       <c r="N22" s="3">
+        <v>46000</v>
+      </c>
+      <c r="O22" s="3">
         <v>69000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>50000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>51000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>54000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>48000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>138000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>50000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>43000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>48000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>59000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>58000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>47000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>90000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>55000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>62000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>55000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>62300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>67000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>72000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>63000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>390000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>72100</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E23" s="3">
         <v>276000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>287000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>102000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>172000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>263000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>141000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>83000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>71000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>152000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>122000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>300000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>411000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1028000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1038000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>501000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-143000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-42000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>44000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>80000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>149000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>243000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>102000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>80000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>186000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>241000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>21000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>218200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>40000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>155000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>113000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>10000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-355900</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E24" s="3">
         <v>41000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-17000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-74000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>28000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>12000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-54000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>29000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>11000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-202000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>40000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>112000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-48000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>55000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-72000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-6000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-264000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>33000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>9000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-41000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>21000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>45000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>42000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>93000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-29000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-119400</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,210 +2447,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E26" s="3">
         <v>235000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>288000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>119000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>246000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>235000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>129000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>137000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>42000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>143000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>111000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>502000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>371000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>916000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1086000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>446000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-71000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-48000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>50000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>344000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>144000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>210000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>93000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>121000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>165000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>196000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>17000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>176200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>80000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>155000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>20000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>39000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-236500</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E27" s="3">
         <v>201000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>234000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>118000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>248000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>154000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>69000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>190000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>166000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>64000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>54000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>398000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>143000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>465000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1072000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>318000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-136000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>27000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>30000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>334000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>111000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>184000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>84000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>57000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>142000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>138000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>17000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>94700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>15000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>103000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>19000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>10000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2702,28 +2759,31 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2738,73 +2798,76 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>5000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-1000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>14000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-58000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-363000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-93000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-128000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-1119000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-4000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>42000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>64000</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>28000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>429000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-3259000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>134000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>64000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-162000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-337000</v>
       </c>
-      <c r="AI29" s="3" t="s">
+      <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2904,8 +2967,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3005,31 +3071,34 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3049,11 +3118,11 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S32" s="3">
         <v>0</v>
@@ -3106,109 +3175,115 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>201000</v>
+        <v>114000</v>
       </c>
       <c r="E33" s="3">
-        <v>234000</v>
+        <v>205000</v>
       </c>
       <c r="F33" s="3">
-        <v>118000</v>
+        <v>251000</v>
       </c>
       <c r="G33" s="3">
-        <v>248000</v>
+        <v>122000</v>
       </c>
       <c r="H33" s="3">
-        <v>154000</v>
+        <v>262000</v>
       </c>
       <c r="I33" s="3">
-        <v>69000</v>
+        <v>158000</v>
       </c>
       <c r="J33" s="3">
+        <v>83000</v>
+      </c>
+      <c r="K33" s="3">
         <v>190000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>166000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>64000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>54000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>403000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>142000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>459000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1086000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>260000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-499000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-66000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-98000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-785000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>107000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>226000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>64000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>121000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>142000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>166000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>446000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>149000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>167000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-143000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-327000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3308,215 +3383,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>201000</v>
+        <v>114000</v>
       </c>
       <c r="E35" s="3">
-        <v>234000</v>
+        <v>205000</v>
       </c>
       <c r="F35" s="3">
-        <v>118000</v>
+        <v>251000</v>
       </c>
       <c r="G35" s="3">
-        <v>248000</v>
+        <v>122000</v>
       </c>
       <c r="H35" s="3">
-        <v>154000</v>
+        <v>262000</v>
       </c>
       <c r="I35" s="3">
-        <v>69000</v>
+        <v>158000</v>
       </c>
       <c r="J35" s="3">
+        <v>83000</v>
+      </c>
+      <c r="K35" s="3">
         <v>190000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>166000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>64000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>54000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>403000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>142000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>459000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1086000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>260000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-499000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-66000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-98000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-785000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>107000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>226000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>64000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>121000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>142000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>166000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>446000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>149000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>167000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-143000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-327000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3552,8 +3636,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3589,132 +3674,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1180000</v>
+        <v>1457000</v>
       </c>
       <c r="E41" s="3">
-        <v>1176000</v>
+        <v>1066000</v>
       </c>
       <c r="F41" s="3">
-        <v>1118000</v>
+        <v>995000</v>
       </c>
       <c r="G41" s="3">
-        <v>917000</v>
+        <v>937000</v>
       </c>
       <c r="H41" s="3">
-        <v>1349000</v>
+        <v>829000</v>
       </c>
       <c r="I41" s="3">
-        <v>824000</v>
+        <v>1195000</v>
       </c>
       <c r="J41" s="3">
+        <v>724000</v>
+      </c>
+      <c r="K41" s="3">
         <v>1007000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>935000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1039000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1125000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1573000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1818000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1850000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1316000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1723000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1136000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1149000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1085000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1249000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1450000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1541000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1340000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1568000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1885000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1620000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1597000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1435000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2072900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2713300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2531300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2229000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2951600</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>298000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>367000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>506000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>483000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>704000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>423000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>309000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3791,50 +3880,53 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>11574000</v>
+        <v>323000</v>
       </c>
       <c r="E43" s="3">
-        <v>11828000</v>
+        <v>300000</v>
       </c>
       <c r="F43" s="3">
-        <v>11982000</v>
+        <v>335000</v>
       </c>
       <c r="G43" s="3">
-        <v>11765000</v>
-      </c>
-      <c r="H43" s="3">
-        <v>12131000</v>
-      </c>
-      <c r="I43" s="3">
-        <v>12438000</v>
-      </c>
-      <c r="J43" s="3">
+        <v>322000</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="3">
         <v>12426000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13561000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13079000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13261000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13635000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13580000</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3847,8 +3939,8 @@
       <c r="T43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -3892,31 +3984,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3993,31 +4088,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>13298000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>13160000</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>13476000</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>13647000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>13296000</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>13899000</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>14330000</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4094,31 +4192,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>15376000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>14893000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>15312000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>15389000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>14810000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>15479000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>15328000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4195,132 +4296,138 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>34226000</v>
+        <v>26895000</v>
       </c>
       <c r="E47" s="3">
-        <v>34615000</v>
+        <v>26353000</v>
       </c>
       <c r="F47" s="3">
-        <v>35683000</v>
+        <v>26599000</v>
       </c>
       <c r="G47" s="3">
-        <v>34886000</v>
+        <v>27352000</v>
       </c>
       <c r="H47" s="3">
-        <v>36406000</v>
+        <v>27003000</v>
       </c>
       <c r="I47" s="3">
-        <v>37813000</v>
+        <v>28304000</v>
       </c>
       <c r="J47" s="3">
+        <v>29534000</v>
+      </c>
+      <c r="K47" s="3">
         <v>38086000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>38408000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>39911000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>41978000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>44387000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>47491000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>45341000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>44660000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>54841000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>54357000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>54264000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>51772000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>52700000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>67153000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>65417000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>64204000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>49918000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>62277000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>62241000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>63014000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>64644000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>93681000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>90575600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>89116700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>61153000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>93051100</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -4373,62 +4480,65 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>8</v>
+      <c r="AB48" s="3">
+        <v>0</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AD48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE48" s="3">
         <v>107000</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AG48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AH48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI48" s="3">
         <v>112300</v>
       </c>
-      <c r="AI48" s="3" t="s">
+      <c r="AJ48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1604000</v>
+        <v>3783000</v>
       </c>
       <c r="E49" s="3">
-        <v>1609000</v>
+        <v>3800000</v>
       </c>
       <c r="F49" s="3">
-        <v>1605000</v>
+        <v>3831000</v>
       </c>
       <c r="G49" s="3">
-        <v>1648000</v>
+        <v>3855000</v>
       </c>
       <c r="H49" s="3">
-        <v>1554000</v>
+        <v>3926000</v>
       </c>
       <c r="I49" s="3">
-        <v>1551000</v>
+        <v>3858000</v>
       </c>
       <c r="J49" s="3">
+        <v>3884000</v>
+      </c>
+      <c r="K49" s="3">
         <v>958000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>824000</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4444,8 +4554,8 @@
       <c r="Q49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -4474,32 +4584,35 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>8</v>
+      <c r="AB49" s="3">
+        <v>0</v>
       </c>
       <c r="AC49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AD49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE49" s="3">
         <v>186000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>196000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>197800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>208000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>219500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>227300</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4599,8 +4712,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4700,109 +4816,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2171000</v>
+        <v>113757000</v>
       </c>
       <c r="E52" s="3">
-        <v>2178000</v>
+        <v>108741000</v>
       </c>
       <c r="F52" s="3">
-        <v>2160000</v>
+        <v>108270000</v>
       </c>
       <c r="G52" s="3">
-        <v>2438000</v>
+        <v>102687000</v>
       </c>
       <c r="H52" s="3">
-        <v>2161000</v>
+        <v>95386000</v>
       </c>
       <c r="I52" s="3">
-        <v>2122000</v>
+        <v>99117000</v>
       </c>
       <c r="J52" s="3">
+        <v>94652000</v>
+      </c>
+      <c r="K52" s="3">
         <v>2223000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1931000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1795000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1405000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>986000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>691000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>690000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>935000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>21889000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>21494000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>21249000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>20902000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>22953000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>401000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>576000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>864000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>21655000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1122000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>58102000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>59833000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1663700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1756900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2055700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>66368800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1128100</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4902,109 +5024,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>166933000</v>
+      </c>
+      <c r="E54" s="3">
         <v>161280000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>161631000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>157085000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>149265000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>154616000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>151208000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>146606000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>144048000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>147520000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>161806000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>171262000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>168417000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>168194000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>162861000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>180518000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>171466000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>166934000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>155732000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>168990000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>166850000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>165162000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>161985000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>155430000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>165036000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>162740000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>219824000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>222532000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>226643900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>219838800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>217025500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>214585000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>218622200</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5040,8 +5168,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5077,31 +5206,32 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5178,37 +5308,40 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>395000</v>
+        <v>1765000</v>
       </c>
       <c r="E58" s="3">
-        <v>393000</v>
+        <v>1610000</v>
       </c>
       <c r="F58" s="3">
-        <v>1000</v>
+        <v>1613000</v>
       </c>
       <c r="G58" s="3">
-        <v>2000</v>
+        <v>1163000</v>
       </c>
       <c r="H58" s="3">
-        <v>143000</v>
+        <v>1192000</v>
       </c>
       <c r="I58" s="3">
-        <v>143000</v>
+        <v>1444000</v>
       </c>
       <c r="J58" s="3">
-        <v>141000</v>
+        <v>1471000</v>
       </c>
       <c r="K58" s="3">
         <v>141000</v>
       </c>
       <c r="L58" s="3">
-        <v>1000</v>
+        <v>141000</v>
       </c>
       <c r="M58" s="3">
         <v>1000</v>
@@ -5244,10 +5377,10 @@
         <v>1000</v>
       </c>
       <c r="X58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y58" s="3">
         <v>97000</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>1000</v>
       </c>
       <c r="Z58" s="3">
         <v>1000</v>
@@ -5259,152 +5392,158 @@
         <v>1000</v>
       </c>
       <c r="AC58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
         <v>337000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>336600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>735900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>735500</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>100362000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>99856000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>94254000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>86681000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>90152000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>85897000</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>81476000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>77358000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>81237000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>94232000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>101616000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>97995000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>98102000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>93872000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>90905000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>83454000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>80129000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>71002000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>83043000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>82049000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>81887000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>79627000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>71297000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>83034000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>80599000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>79668000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>79471000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>111603200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>105725300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>103261300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>67883100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>101627000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1765000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1610000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>1613000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>1163000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>1192000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>1444000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1471000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5481,210 +5620,219 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1707000</v>
+        <v>2441000</v>
       </c>
       <c r="E61" s="3">
-        <v>1707000</v>
+        <v>2015000</v>
       </c>
       <c r="F61" s="3">
-        <v>2097000</v>
+        <v>2025000</v>
       </c>
       <c r="G61" s="3">
-        <v>2095000</v>
+        <v>2577000</v>
       </c>
       <c r="H61" s="3">
-        <v>2095000</v>
+        <v>2448000</v>
       </c>
       <c r="I61" s="3">
-        <v>2094000</v>
+        <v>2485000</v>
       </c>
       <c r="J61" s="3">
-        <v>2094000</v>
+        <v>2461000</v>
       </c>
       <c r="K61" s="3">
         <v>2094000</v>
       </c>
       <c r="L61" s="3">
+        <v>2094000</v>
+      </c>
+      <c r="M61" s="3">
         <v>2385000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2406000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2595000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2970000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>2969000</v>
       </c>
       <c r="Q61" s="3">
         <v>2969000</v>
       </c>
       <c r="R61" s="3">
+        <v>2969000</v>
+      </c>
+      <c r="S61" s="3">
         <v>3044000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>3043000</v>
       </c>
       <c r="T61" s="3">
         <v>3043000</v>
       </c>
       <c r="U61" s="3">
-        <v>3042000</v>
+        <v>3043000</v>
       </c>
       <c r="V61" s="3">
         <v>3042000</v>
       </c>
       <c r="W61" s="3">
-        <v>3041000</v>
+        <v>3042000</v>
       </c>
       <c r="X61" s="3">
         <v>3041000</v>
       </c>
       <c r="Y61" s="3">
-        <v>3136000</v>
+        <v>3041000</v>
       </c>
       <c r="Z61" s="3">
         <v>3136000</v>
       </c>
       <c r="AA61" s="3">
+        <v>3136000</v>
+      </c>
+      <c r="AB61" s="3">
         <v>3459000</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>3458000</v>
       </c>
       <c r="AC61" s="3">
         <v>3458000</v>
       </c>
       <c r="AD61" s="3">
+        <v>3458000</v>
+      </c>
+      <c r="AE61" s="3">
         <v>3123000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3122200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2726200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2725700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3550000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3548500</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="D62" s="3">
+        <v>156145000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>151786000</v>
+      </c>
+      <c r="F62" s="3">
+        <v>152122000</v>
+      </c>
+      <c r="G62" s="3">
+        <v>146942000</v>
+      </c>
+      <c r="H62" s="3">
+        <v>140666000</v>
+      </c>
+      <c r="I62" s="3">
+        <v>145159000</v>
+      </c>
+      <c r="J62" s="3">
+        <v>141589000</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>196000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>205000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>213000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>226000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>274000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>304000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>333000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>18976000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>18607000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>18465000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>18414000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>18966000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>409000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>445000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>465000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>18454000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>516000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>527000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>56998000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>58827000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>542200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>636800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>656000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>60250000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>631400</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5784,8 +5932,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5885,8 +6036,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5986,109 +6140,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>157237000</v>
+        <v>160351000</v>
       </c>
       <c r="E66" s="3">
-        <v>157478000</v>
+        <v>155411000</v>
       </c>
       <c r="F66" s="3">
-        <v>152892000</v>
+        <v>155760000</v>
       </c>
       <c r="G66" s="3">
-        <v>146138000</v>
+        <v>151032000</v>
       </c>
       <c r="H66" s="3">
-        <v>150919000</v>
+        <v>144306000</v>
       </c>
       <c r="I66" s="3">
-        <v>147254000</v>
+        <v>149088000</v>
       </c>
       <c r="J66" s="3">
+        <v>145521000</v>
+      </c>
+      <c r="K66" s="3">
         <v>143257000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>139955000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>143004000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>155608000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>163009000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>160028000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>159832000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>154930000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>170408000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>161809000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>157386000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>148305000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>159651000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>156299000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>155098000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>152920000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>147217000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>156513000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>154280000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>210446000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>212523000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>212990900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>206486600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>204135100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>201590000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>203416200</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6124,8 +6284,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6225,8 +6386,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6326,8 +6490,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6427,8 +6594,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6528,109 +6698,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>907000</v>
+      </c>
+      <c r="E72" s="3">
         <v>855000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>697000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>505000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>302000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>40000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-118000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-201000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-994000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1201000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1269000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1310000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-3238000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3394000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3857000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-4957000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-5152000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-4833000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-4766000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-4718000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-11665000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-11785000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-12011000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-11732000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-11853000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-11995000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-12161000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-12719000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-9655600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-9804200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-9971400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-9742000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-9310300</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6730,8 +6906,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6831,8 +7010,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6932,109 +7114,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4719000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4043000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4153000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4193000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3127000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3697000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3954000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3349000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4093000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4516000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6198000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8253000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8389000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8362000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7931000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10110000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9657000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9548000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7427000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9339000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10551000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10064000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9065000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8213000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8523000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8460000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9378000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10009000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13653000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13352200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12890400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12995000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>15206000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7134,215 +7322,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>201000</v>
+        <v>114000</v>
       </c>
       <c r="E81" s="3">
-        <v>234000</v>
+        <v>205000</v>
       </c>
       <c r="F81" s="3">
-        <v>118000</v>
+        <v>251000</v>
       </c>
       <c r="G81" s="3">
-        <v>248000</v>
+        <v>122000</v>
       </c>
       <c r="H81" s="3">
-        <v>154000</v>
+        <v>262000</v>
       </c>
       <c r="I81" s="3">
-        <v>69000</v>
+        <v>158000</v>
       </c>
       <c r="J81" s="3">
+        <v>83000</v>
+      </c>
+      <c r="K81" s="3">
         <v>190000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>166000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>64000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>54000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>403000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>142000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>459000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1086000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>260000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-499000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-66000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-98000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-785000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>107000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>226000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>64000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>121000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>142000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>166000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>446000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>149000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>167000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-143000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-327000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7378,31 +7575,32 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+        <v>-22000</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7479,8 +7677,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7580,8 +7781,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7681,8 +7885,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7782,8 +7989,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7883,8 +8093,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7984,109 +8197,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>719000</v>
+      </c>
+      <c r="E89" s="3">
         <v>316000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>231000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>364000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>403000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>715000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>156000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>219000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>418000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>296000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>419000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>140000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>121000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>747000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-936000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>421000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>788000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>508000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-76000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>459000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>302000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>418000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>131000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>234000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>580000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>653000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>401000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>456000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>570000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>605800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-49800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3591000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>819700</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8122,31 +8341,32 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8205,26 +8425,29 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-9700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-10400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-66700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-25800</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8324,8 +8547,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8425,109 +8651,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-486000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-92000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1082000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>833000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>430000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>797000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>472000</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-372000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-403000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-578000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-600000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>181000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>670000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-636000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1825000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-139000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-811000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-374000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-954000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>117000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-44000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-333000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-36000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-149000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>236000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-145000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1581300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-892500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>190800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3683000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1924000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8563,109 +8795,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>43000</v>
+      </c>
+      <c r="F96" s="3">
+        <v>41000</v>
+      </c>
+      <c r="G96" s="3">
+        <v>42000</v>
+      </c>
+      <c r="H96" s="3">
+        <v>42000</v>
+      </c>
+      <c r="I96" s="3">
+        <v>23000</v>
+      </c>
+      <c r="J96" s="3">
         <v>20000</v>
       </c>
-      <c r="E96" s="3">
-        <v>-41000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-42000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-42000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-23000</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>-20000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="M96" s="3">
         <v>-20000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-20000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-21000</v>
       </c>
       <c r="N96" s="3">
         <v>-21000</v>
       </c>
       <c r="O96" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-19000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-20000</v>
       </c>
       <c r="Q96" s="3">
         <v>-20000</v>
       </c>
       <c r="R96" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-18000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-58000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-19000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-20000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-21000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-20000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-1000</v>
       </c>
       <c r="Z96" s="3">
         <v>-1000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1700</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-1900</v>
       </c>
       <c r="AG96" s="3">
         <v>-1900</v>
       </c>
       <c r="AH96" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8765,8 +9001,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8866,8 +9105,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8967,132 +9209,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-220000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1255000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-996000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1265000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-987000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-811000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-147000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-150000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>732000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-407000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-55000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>391000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-333000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-268000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>588000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1114000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-158000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>727000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>11000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>546000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-86000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-592000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-289000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-926000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-397000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-562400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>414200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>556600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-753400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>495400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>71300</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9169,105 +9417,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>365000</v>
+      </c>
+      <c r="E102" s="3">
         <v>4000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>58000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>201000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-432000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>525000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-183000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>72000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-104000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-143000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-391000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-493000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-88000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>595000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-534000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>373000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>77000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>211000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-160000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>96000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-106000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>449000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-505000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-251000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>255000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-422000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>240000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-251200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-600500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>269100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-612400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>398000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1033000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>VOYA</t>
   </si>
@@ -656,443 +656,455 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2010000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1956000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2033000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2051000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1819000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1823000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1871000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1835000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1538000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1345000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1524000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1506000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1677000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2009000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2503000</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T8" s="3">
         <v>2231000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5505000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1719000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1705000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1844000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1878000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1972000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1848000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>837000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2259000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2114000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1981000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1281400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2185000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2192000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2059000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8822000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2541200</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1043000</v>
+      </c>
+      <c r="E9" s="3">
         <v>993000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>899000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>907000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>861000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>856000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>739000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>810000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>83000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>60000</v>
-      </c>
-      <c r="M9" s="3">
-        <v>62000</v>
       </c>
       <c r="N9" s="3">
         <v>62000</v>
       </c>
       <c r="O9" s="3">
+        <v>62000</v>
+      </c>
+      <c r="P9" s="3">
         <v>40000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>190000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>539000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>16000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>336000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>76000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>46000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>36000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>43000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>57000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>-27000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>86000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>74000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>100000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>-34400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>209000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>195000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>64000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>415000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>967000</v>
+      </c>
+      <c r="E10" s="3">
         <v>963000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1134000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1144000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>958000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>967000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1132000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1025000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1455000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1285000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1462000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1444000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1637000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1819000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2477000</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T10" s="3">
         <v>2215000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5169000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1700000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1629000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1798000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1842000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1929000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1791000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>864000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2173000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2040000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1881000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1315800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1976000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1997000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1995000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8407000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2360500</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1129,8 +1141,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1233,8 +1246,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1337,13 +1353,16 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>3000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1351,83 +1370,83 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>55000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
+        <v>70000</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>12000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>80000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>15000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>10000</v>
-      </c>
-      <c r="O14" s="3">
-        <v>3000</v>
       </c>
       <c r="P14" s="3">
         <v>3000</v>
       </c>
       <c r="Q14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="R14" s="3">
         <v>13000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>1000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>80000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>50000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>20000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>31000</v>
-      </c>
-      <c r="X14" s="3">
-        <v>3000</v>
       </c>
       <c r="Y14" s="3">
         <v>3000</v>
       </c>
       <c r="Z14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AA14" s="3">
         <v>26000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>6000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>7000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>14000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>15800</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>1000</v>
       </c>
       <c r="AG14" s="3">
         <v>1000</v>
@@ -1436,40 +1455,43 @@
         <v>1000</v>
       </c>
       <c r="AI14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>34000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E15" s="3">
         <v>24000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>23000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>21300</v>
       </c>
       <c r="G15" s="3">
         <v>21300</v>
       </c>
       <c r="H15" s="3">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="I15" s="3">
         <v>21000</v>
       </c>
       <c r="J15" s="3">
+        <v>21000</v>
+      </c>
+      <c r="K15" s="3">
         <v>9000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1545,8 +1567,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1580,216 +1605,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1812000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1771000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1659000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1707000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1582000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1567000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1575000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1502000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1644000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1407000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1231000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1326000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1338000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1308000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1548000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1424000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-3049000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1682000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5510000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1711000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1618000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1716000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1670000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1671000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1699000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>667000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2018000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1811000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1905000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1000900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2078000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1965000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1883000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8422000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E18" s="3">
         <v>185000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>374000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>344000</v>
       </c>
-      <c r="G18" s="3">
-        <v>237000</v>
-      </c>
       <c r="H18" s="3">
+        <v>252000</v>
+      </c>
+      <c r="I18" s="3">
         <v>248000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>369000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>191000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>131000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>114000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>198000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>168000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>369000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>461000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1079000</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T18" s="3">
         <v>549000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>8000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>87000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>128000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>208000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>301000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>149000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>170000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>241000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>303000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>76000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>280500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>107000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>227000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>176000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>400000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-283800</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1826,8 +1858,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1852,8 +1885,8 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1873,11 +1906,11 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -1930,47 +1963,50 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>224000</v>
+      </c>
+      <c r="E21" s="3">
         <v>209000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>397000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>365300</v>
       </c>
-      <c r="G21" s="3">
-        <v>258300</v>
-      </c>
       <c r="H21" s="3">
+        <v>274000</v>
+      </c>
+      <c r="I21" s="3">
         <v>269000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>390000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>200000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>130000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="3">
         <v>179000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1980,15 +2016,15 @@
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T21" s="3">
         <v>549000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2034,320 +2070,332 @@
       <c r="AJ21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E22" s="3">
         <v>69000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>98000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>57000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>80000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>76000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>94000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>48000</v>
       </c>
       <c r="K22" s="3">
         <v>48000</v>
       </c>
       <c r="L22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="M22" s="3">
         <v>43000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>46000</v>
       </c>
       <c r="N22" s="3">
         <v>46000</v>
       </c>
       <c r="O22" s="3">
+        <v>46000</v>
+      </c>
+      <c r="P22" s="3">
         <v>69000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>50000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>51000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>54000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>48000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>138000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>50000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>43000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>48000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>59000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>58000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>47000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>90000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>55000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>62000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>55000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>62300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>67000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>72000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>63000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>390000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>72100</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E23" s="3">
         <v>116000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>276000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>287000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>102000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>172000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>263000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>141000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>83000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>71000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>152000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>122000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>300000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>411000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1028000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1038000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>501000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-143000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-42000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>44000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>80000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>149000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>243000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>102000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>80000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>186000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>241000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>21000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>218200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>40000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>155000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>113000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-355900</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>18000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>41000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-17000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-74000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>28000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-54000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>29000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-202000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>40000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>112000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-48000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>55000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-72000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-6000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-264000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>33000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>9000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>21000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>45000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>42000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
       <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
         <v>93000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-29000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-119400</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2450,216 +2498,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E26" s="3">
         <v>98000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>235000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>288000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>119000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>246000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>235000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>129000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>137000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>42000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>143000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>111000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>502000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>371000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>916000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1086000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>446000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-71000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-48000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>50000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>344000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>144000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>210000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>93000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>121000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>165000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>196000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>17000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>176200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>80000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>155000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>20000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>39000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-236500</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E27" s="3">
         <v>98000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>201000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>234000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>118000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>248000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>154000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>69000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>190000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>166000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>64000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>54000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>398000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>143000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>465000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1072000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>318000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-136000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>27000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>30000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>334000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>111000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>184000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>84000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>57000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>142000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>138000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>17000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>94700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>15000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>103000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>19000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2762,8 +2819,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2801,73 +2861,76 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>5000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-6000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>14000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-58000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-363000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-93000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-128000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-1119000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>42000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>64000</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>28000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>429000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-3259000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>134000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>64000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-162000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-337000</v>
       </c>
-      <c r="AJ29" s="3" t="s">
+      <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2970,8 +3033,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3074,8 +3140,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3100,8 +3169,8 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -3121,11 +3190,11 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T32" s="3">
         <v>0</v>
@@ -3178,112 +3247,118 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E33" s="3">
         <v>114000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>205000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>251000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>122000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>262000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>158000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>83000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>190000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>166000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>64000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>54000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>403000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>142000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>459000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1086000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>260000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-499000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-66000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-98000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-785000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>107000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>226000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>64000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>121000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>142000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>166000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>446000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>149000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>167000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-143000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-327000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3386,221 +3461,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E35" s="3">
         <v>114000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>205000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>251000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>122000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>262000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>158000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>83000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>190000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>166000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>64000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>54000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>403000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>142000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>459000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1086000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>260000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-499000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-66000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-98000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-785000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>107000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>226000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>64000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>121000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>142000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>166000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>446000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>149000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>167000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-143000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-327000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3637,8 +3721,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3675,139 +3760,143 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1399000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1457000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1066000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>995000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>937000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>829000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1195000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>724000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1007000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>935000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1039000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1125000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1573000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1818000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1850000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1316000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1723000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1136000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1149000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1085000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1249000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1450000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1541000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1340000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1568000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1885000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1620000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1597000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1435000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2072900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2713300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2531300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2229000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2951600</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>340000</v>
+      </c>
+      <c r="E42" s="3">
         <v>298000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>367000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>506000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>483000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>704000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>423000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>309000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3883,53 +3972,56 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>338000</v>
+      </c>
+      <c r="E43" s="3">
         <v>323000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>300000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>335000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>322000</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L43" s="3">
         <v>12426000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13561000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13079000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13261000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13635000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13580000</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3942,8 +4034,8 @@
       <c r="U43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -3987,8 +4079,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4013,8 +4108,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4091,35 +4186,38 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12917000</v>
+      </c>
+      <c r="E45" s="3">
         <v>13298000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13160000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13476000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13647000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13296000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13899000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14330000</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -4195,35 +4293,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14994000</v>
+      </c>
+      <c r="E46" s="3">
         <v>15376000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14893000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15312000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15389000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14810000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15479000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15328000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4299,112 +4400,118 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>26015000</v>
+      </c>
+      <c r="E47" s="3">
         <v>26895000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>26353000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>26599000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>27352000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>27003000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>28304000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>29534000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>38086000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>38408000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>39911000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>41978000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>44387000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>47491000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>45341000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>44660000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>54841000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>54357000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>54264000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>51772000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>52700000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>67153000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>65417000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>64204000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>49918000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>62277000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>62241000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>63014000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>64644000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>93681000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>90575600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>89116700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>61153000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>93051100</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4429,8 +4536,8 @@
       <c r="J48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -4483,65 +4590,68 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>8</v>
+      <c r="AC48" s="3">
+        <v>0</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF48" s="3">
         <v>107000</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>112300</v>
       </c>
-      <c r="AJ48" s="3" t="s">
+      <c r="AK48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3728000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3783000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3800000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3831000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3855000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3926000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3858000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3884000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>958000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>824000</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4557,8 +4667,8 @@
       <c r="R49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -4587,32 +4697,35 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>8</v>
+      <c r="AC49" s="3">
+        <v>0</v>
       </c>
       <c r="AD49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AE49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF49" s="3">
         <v>186000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>196000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>197800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>208000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>219500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>227300</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4715,8 +4828,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4819,112 +4935,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>111896000</v>
+      </c>
+      <c r="E52" s="3">
         <v>113757000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>108741000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>108270000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>102687000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>95386000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>99117000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>94652000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2223000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1931000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1795000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1405000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>986000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>691000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>690000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>935000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>21889000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>21494000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>21249000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>20902000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>22953000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>401000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>576000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>864000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>21655000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1122000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>58102000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>59833000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1663700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1756900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2055700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>66368800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1128100</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5027,112 +5149,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>163889000</v>
+      </c>
+      <c r="E54" s="3">
         <v>166933000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>161280000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>161631000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>157085000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>149265000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>154616000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>151208000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>146606000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>144048000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>147520000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>161806000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>171262000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>168417000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>168194000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>162861000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>180518000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>171466000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>166934000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>155732000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>168990000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>166850000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>165162000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>161985000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>155430000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>165036000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>162740000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>219824000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>222532000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>226643900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>219838800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>217025500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>214585000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>218622200</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5169,8 +5297,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5207,8 +5336,9 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5233,8 +5363,8 @@
       <c r="J57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -5311,40 +5441,43 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1743000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1765000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1610000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1613000</v>
       </c>
-      <c r="G58" s="3">
-        <v>1163000</v>
-      </c>
       <c r="H58" s="3">
+        <v>1122000</v>
+      </c>
+      <c r="I58" s="3">
         <v>1192000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1444000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1471000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>141000</v>
       </c>
       <c r="L58" s="3">
         <v>141000</v>
       </c>
       <c r="M58" s="3">
-        <v>1000</v>
+        <v>141000</v>
       </c>
       <c r="N58" s="3">
         <v>1000</v>
@@ -5380,10 +5513,10 @@
         <v>1000</v>
       </c>
       <c r="Y58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z58" s="3">
         <v>97000</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>1000</v>
       </c>
       <c r="AA58" s="3">
         <v>1000</v>
@@ -5395,28 +5528,31 @@
         <v>1000</v>
       </c>
       <c r="AD58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3">
         <v>337000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>336600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>735900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>735500</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5441,113 +5577,116 @@
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>81476000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>77358000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>81237000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>94232000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>101616000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>97995000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>98102000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>93872000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>90905000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>83454000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>80129000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>71002000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>83043000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>82049000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>81887000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>79627000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>71297000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>83034000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>80599000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>79668000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>79471000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>111603200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>105725300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>103261300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>67883100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>101627000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1743000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1765000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1610000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1613000</v>
       </c>
-      <c r="G60" s="3">
-        <v>1163000</v>
-      </c>
       <c r="H60" s="3">
+        <v>1122000</v>
+      </c>
+      <c r="I60" s="3">
         <v>1192000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1444000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1471000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5623,216 +5762,225 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2567000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2441000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2015000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2025000</v>
       </c>
-      <c r="G61" s="3">
-        <v>2577000</v>
-      </c>
       <c r="H61" s="3">
+        <v>2451000</v>
+      </c>
+      <c r="I61" s="3">
         <v>2448000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2485000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2461000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>2094000</v>
       </c>
       <c r="L61" s="3">
         <v>2094000</v>
       </c>
       <c r="M61" s="3">
+        <v>2094000</v>
+      </c>
+      <c r="N61" s="3">
         <v>2385000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2406000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2595000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2970000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>2969000</v>
       </c>
       <c r="R61" s="3">
         <v>2969000</v>
       </c>
       <c r="S61" s="3">
+        <v>2969000</v>
+      </c>
+      <c r="T61" s="3">
         <v>3044000</v>
-      </c>
-      <c r="T61" s="3">
-        <v>3043000</v>
       </c>
       <c r="U61" s="3">
         <v>3043000</v>
       </c>
       <c r="V61" s="3">
-        <v>3042000</v>
+        <v>3043000</v>
       </c>
       <c r="W61" s="3">
         <v>3042000</v>
       </c>
       <c r="X61" s="3">
-        <v>3041000</v>
+        <v>3042000</v>
       </c>
       <c r="Y61" s="3">
         <v>3041000</v>
       </c>
       <c r="Z61" s="3">
-        <v>3136000</v>
+        <v>3041000</v>
       </c>
       <c r="AA61" s="3">
         <v>3136000</v>
       </c>
       <c r="AB61" s="3">
+        <v>3136000</v>
+      </c>
+      <c r="AC61" s="3">
         <v>3459000</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>3458000</v>
       </c>
       <c r="AD61" s="3">
         <v>3458000</v>
       </c>
       <c r="AE61" s="3">
+        <v>3458000</v>
+      </c>
+      <c r="AF61" s="3">
         <v>3123000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3122200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2726200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2725700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3550000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3548500</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>153241000</v>
+      </c>
+      <c r="E62" s="3">
         <v>156145000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>151786000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>152122000</v>
       </c>
-      <c r="G62" s="3">
-        <v>146942000</v>
-      </c>
       <c r="H62" s="3">
+        <v>147109000</v>
+      </c>
+      <c r="I62" s="3">
         <v>140666000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>145159000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>141589000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>196000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>205000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>213000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>226000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>274000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>304000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>333000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>18976000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>18607000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>18465000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>18414000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>18966000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>409000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>445000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>465000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>18454000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>516000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>527000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>56998000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>58827000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>542200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>636800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>656000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>60250000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>631400</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5935,8 +6083,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6039,8 +6190,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6143,112 +6297,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>157882000</v>
+      </c>
+      <c r="E66" s="3">
         <v>160351000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>155411000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>155760000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>151032000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>144306000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>149088000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>145521000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>143257000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>139955000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>143004000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>155608000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>163009000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>160028000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>159832000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>154930000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>170408000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>161809000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>157386000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>148305000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>159651000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>156299000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>155098000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>152920000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>147217000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>156513000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>154280000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>210446000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>212523000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>212990900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>206486600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>204135100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>201590000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>203416200</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6285,8 +6445,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6389,8 +6550,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6493,8 +6657,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6597,8 +6764,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6701,112 +6871,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>954000</v>
+      </c>
+      <c r="E72" s="3">
         <v>907000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>855000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>697000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>505000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>302000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>40000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-118000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-201000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-994000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1201000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1269000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1310000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-3238000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3394000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3857000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-4957000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-5152000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-4833000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-4766000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-4718000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-11665000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-11785000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-12011000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-11732000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-11853000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-11995000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-12161000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-12719000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-9655600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-9804200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-9971400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-9742000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-9310300</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6909,8 +7085,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7013,8 +7192,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7117,112 +7299,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4005000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4719000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4043000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4153000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4193000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3127000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3697000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3954000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3349000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4093000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4516000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6198000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8253000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8389000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8362000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7931000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>10110000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9657000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9548000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7427000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9339000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10551000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10064000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9065000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8213000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8523000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8460000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9378000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>10009000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13653000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>13352200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12890400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12995000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>15206000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7325,221 +7513,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E81" s="3">
         <v>114000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>205000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>251000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>122000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>262000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>158000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>83000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>190000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>166000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>64000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>54000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>403000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>142000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>459000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1086000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>260000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-499000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-66000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-98000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-785000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>107000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>226000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>64000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>121000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>142000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>166000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>446000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>149000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>167000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-143000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-327000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7576,8 +7773,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7593,17 +7791,17 @@
       <c r="G83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3">
         <v>-22000</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -7680,8 +7878,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7784,8 +7985,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7888,8 +8092,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7992,8 +8199,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8096,8 +8306,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8200,112 +8413,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E89" s="3">
         <v>719000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>316000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>231000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>364000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>403000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>715000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>156000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>219000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>418000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>296000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>419000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>140000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>121000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>747000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-936000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>421000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>788000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>508000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-76000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>459000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>302000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>418000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>131000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>234000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>580000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>653000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>401000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>456000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>570000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>605800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-49800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3591000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>819700</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8342,8 +8561,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8368,8 +8588,8 @@
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8428,26 +8648,29 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-9700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-10400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-66700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-25800</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8550,8 +8773,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8654,112 +8880,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-486000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-92000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1082000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>833000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>430000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>797000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>472000</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-372000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-403000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-578000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-600000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>181000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>670000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-636000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1825000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-139000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-811000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-374000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-954000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>117000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-44000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-333000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-36000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-149000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>236000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-145000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1581300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-892500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>190800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3683000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1924000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8796,112 +9028,116 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E96" s="3">
         <v>44000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>43000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>41000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>42000</v>
       </c>
       <c r="H96" s="3">
         <v>42000</v>
       </c>
       <c r="I96" s="3">
+        <v>42000</v>
+      </c>
+      <c r="J96" s="3">
         <v>23000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>20000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-20000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-22000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-20000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-21000</v>
       </c>
       <c r="O96" s="3">
         <v>-21000</v>
       </c>
       <c r="P96" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-19000</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-20000</v>
       </c>
       <c r="R96" s="3">
         <v>-20000</v>
       </c>
       <c r="S96" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-18000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-58000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-19000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-20000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-21000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-1000</v>
       </c>
       <c r="AA96" s="3">
         <v>-1000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1700</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-1900</v>
       </c>
       <c r="AH96" s="3">
         <v>-1900</v>
       </c>
       <c r="AI96" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9004,8 +9240,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9108,8 +9347,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9212,112 +9454,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-87000</v>
+      </c>
+      <c r="E100" s="3">
         <v>132000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-220000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1255000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-996000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1265000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-987000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-811000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-147000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-150000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>732000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-407000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-55000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>391000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-333000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-268000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>588000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1114000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-158000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>727000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>11000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>546000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-86000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-592000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-289000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-926000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-397000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-562400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>414200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>556600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-753400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>495400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>71300</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9342,8 +9590,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9420,108 +9668,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E102" s="3">
         <v>365000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>58000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>201000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-432000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>525000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-183000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>72000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-104000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-143000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-391000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-493000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-88000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>595000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-534000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>373000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>77000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>211000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-160000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>96000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-106000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>449000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-505000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-251000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>255000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-422000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>240000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-251200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-600500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>269100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-612400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>398000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1033000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
   <si>
     <t>VOYA</t>
   </si>
@@ -656,455 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1969000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2010000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1956000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2033000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2051000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1819000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1823000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1871000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1835000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1538000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1345000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1524000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1506000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1677000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2009000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2503000</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T8" s="3">
+      <c r="T8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U8" s="3">
         <v>2231000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5505000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1719000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1705000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1844000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1878000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1972000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1848000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>837000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2259000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2114000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1981000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1281400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2185000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2192000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2059000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>8822000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2541200</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>897000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1043000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>993000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>899000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>907000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>861000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>856000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>739000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>810000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>83000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>60000</v>
-      </c>
-      <c r="N9" s="3">
-        <v>62000</v>
       </c>
       <c r="O9" s="3">
         <v>62000</v>
       </c>
       <c r="P9" s="3">
+        <v>62000</v>
+      </c>
+      <c r="Q9" s="3">
         <v>40000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>190000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>539000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>16000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>336000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>19000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>76000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>46000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>36000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>43000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>57000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>-27000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>86000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>74000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>100000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>-34400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>209000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>195000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>64000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>415000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1072000</v>
+      </c>
+      <c r="E10" s="3">
         <v>967000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>963000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1134000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1144000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>958000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>967000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1132000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1025000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1455000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1285000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1462000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1444000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1637000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1819000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2477000</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U10" s="3">
         <v>2215000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5169000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1700000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1629000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1798000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1842000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1929000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1791000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>864000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2173000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2040000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1881000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1315800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1976000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1997000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1995000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>8407000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2360500</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1142,8 +1154,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1249,8 +1262,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1356,100 +1372,103 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>3000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>70000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>12000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>80000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>15000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>10000</v>
-      </c>
-      <c r="P14" s="3">
-        <v>3000</v>
       </c>
       <c r="Q14" s="3">
         <v>3000</v>
       </c>
       <c r="R14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="S14" s="3">
         <v>13000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>1000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>80000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>50000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>20000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>31000</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>3000</v>
       </c>
       <c r="Z14" s="3">
         <v>3000</v>
       </c>
       <c r="AA14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AB14" s="3">
         <v>26000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>6000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>7000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>14000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>15800</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>1000</v>
       </c>
       <c r="AH14" s="3">
         <v>1000</v>
@@ -1458,43 +1477,46 @@
         <v>1000</v>
       </c>
       <c r="AJ14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AK14" s="3">
         <v>34000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E15" s="3">
         <v>26000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>24000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>23000</v>
       </c>
-      <c r="G15" s="3">
-        <v>21300</v>
-      </c>
       <c r="H15" s="3">
+        <v>23000</v>
+      </c>
+      <c r="I15" s="3">
         <v>22000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>21000</v>
       </c>
       <c r="J15" s="3">
         <v>21000</v>
       </c>
       <c r="K15" s="3">
+        <v>21000</v>
+      </c>
+      <c r="L15" s="3">
         <v>9000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1570,8 +1592,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,222 +1631,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1729000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1812000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1771000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1659000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1707000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1567000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1575000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1502000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1644000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1407000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1231000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1326000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1338000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1308000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1548000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1424000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-3049000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1682000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5510000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1711000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1618000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1716000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1670000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1671000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1699000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>667000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2018000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1811000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1905000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1000900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2078000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1965000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1883000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8422000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>240000</v>
+      </c>
+      <c r="E18" s="3">
         <v>198000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>185000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>374000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>344000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>252000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>248000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>369000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>191000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>131000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>114000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>198000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>168000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>369000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>461000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1079000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U18" s="3">
         <v>549000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>8000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>87000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>128000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>208000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>301000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>149000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>170000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>241000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>303000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>76000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>280500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>107000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>227000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>176000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>400000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-283800</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1859,8 +1891,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1888,8 +1921,8 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1909,11 +1942,11 @@
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
@@ -1966,50 +1999,53 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>265000</v>
+      </c>
+      <c r="E21" s="3">
         <v>224000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>209000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>397000</v>
       </c>
-      <c r="G21" s="3">
-        <v>365300</v>
-      </c>
       <c r="H21" s="3">
+        <v>367000</v>
+      </c>
+      <c r="I21" s="3">
         <v>274000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>269000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>390000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>200000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>130000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>179000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2019,15 +2055,15 @@
       <c r="S21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U21" s="3">
         <v>549000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-5000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2073,329 +2109,341 @@
       <c r="AK21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E22" s="3">
         <v>75000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>69000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>98000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>57000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>80000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>76000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>94000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>48000</v>
       </c>
       <c r="L22" s="3">
         <v>48000</v>
       </c>
       <c r="M22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="N22" s="3">
         <v>43000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>46000</v>
       </c>
       <c r="O22" s="3">
         <v>46000</v>
       </c>
       <c r="P22" s="3">
+        <v>46000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>69000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>50000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>51000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>54000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>48000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>138000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>50000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>43000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>48000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>59000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>58000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>47000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>90000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>55000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>62000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>55000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>62300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>67000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>72000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>63000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>390000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>72100</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E23" s="3">
         <v>120000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>116000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>276000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>287000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>102000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>172000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>263000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>141000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>83000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>71000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>152000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>122000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>300000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>411000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1028000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1038000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>501000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-143000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-42000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>44000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>80000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>149000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>243000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>102000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>80000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>186000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>241000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>21000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>218200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>40000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>155000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>113000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>10000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-355900</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>18000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>41000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-17000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-74000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>28000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-54000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>29000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-202000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>40000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>112000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-48000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>55000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-72000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-6000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-264000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>33000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>9000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-41000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>21000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>45000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>42000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
       <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>93000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-29000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-119400</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2501,222 +2549,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E26" s="3">
         <v>121000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>98000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>235000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>288000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>119000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>246000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>235000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>129000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>137000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>42000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>143000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>111000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>502000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>371000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>916000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1086000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>446000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-71000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-48000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>50000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>344000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>144000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>210000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>93000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>121000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>165000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>196000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>17000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>176200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>80000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>155000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>39000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-236500</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>139000</v>
+      </c>
+      <c r="E27" s="3">
         <v>93000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>98000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>201000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>234000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>118000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>248000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>154000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>69000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>190000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>166000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>64000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>54000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>398000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>143000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>465000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1072000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>318000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-136000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>27000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>30000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>334000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>111000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>184000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>84000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>57000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>142000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>138000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>17000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>94700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>15000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>103000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>19000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>10000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2822,8 +2879,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2864,73 +2924,76 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>5000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-1000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-6000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>14000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-58000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-363000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-93000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-128000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-1119000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>42000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>64000</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>28000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>429000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-3259000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>134000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>64000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-162000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-337000</v>
       </c>
-      <c r="AK29" s="3" t="s">
+      <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3036,8 +3099,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3143,8 +3209,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3172,8 +3241,8 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3193,11 +3262,11 @@
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U32" s="3">
         <v>0</v>
@@ -3250,115 +3319,121 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>156000</v>
+      </c>
+      <c r="E33" s="3">
         <v>97000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>114000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>205000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>251000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>122000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>262000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>158000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>83000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>190000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>166000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>64000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>54000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>403000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>142000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>459000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1086000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>260000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-499000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-66000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-98000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-785000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>107000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>226000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>64000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>121000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>142000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>166000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>446000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>149000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>167000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-143000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-327000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3464,227 +3539,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>156000</v>
+      </c>
+      <c r="E35" s="3">
         <v>97000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>114000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>205000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>251000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>122000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>262000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>158000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>83000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>190000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>166000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>64000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>54000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>403000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>142000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>459000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1086000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>260000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-499000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-66000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-98000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-785000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>107000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>226000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>64000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>121000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>142000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>166000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>446000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>149000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>167000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-143000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-327000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3722,8 +3806,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3761,145 +3846,149 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>868000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1399000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1457000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1066000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>995000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>937000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>829000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1195000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>724000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1007000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>935000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1039000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1125000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1573000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1818000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1850000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1316000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1723000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1136000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1149000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1085000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1249000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1450000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1541000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1340000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1568000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1885000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1620000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1597000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1435000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2072900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2713300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2531300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2229000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2951600</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>357000</v>
+      </c>
+      <c r="E42" s="3">
         <v>340000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>298000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>367000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>506000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>483000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>704000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>423000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>309000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3975,56 +4064,59 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>334000</v>
+      </c>
+      <c r="E43" s="3">
         <v>338000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>323000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>300000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>335000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>322000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="3">
         <v>12426000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13561000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13079000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13261000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13635000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13580000</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4037,8 +4129,8 @@
       <c r="V43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -4082,8 +4174,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4111,8 +4206,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4189,38 +4284,41 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12809000</v>
+      </c>
+      <c r="E45" s="3">
         <v>12917000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13298000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13160000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13476000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13647000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13296000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13899000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14330000</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -4296,38 +4394,41 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14368000</v>
+      </c>
+      <c r="E46" s="3">
         <v>14994000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15376000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14893000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15312000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15389000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14810000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15479000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15328000</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4403,115 +4504,121 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>27883000</v>
+      </c>
+      <c r="E47" s="3">
         <v>26015000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>26895000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>26353000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>26599000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>27352000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>27003000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28304000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>29534000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>38086000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>38408000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>39911000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>41978000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>44387000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>47491000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>45341000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>44660000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>54841000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>54357000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>54264000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>51772000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>52700000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>67153000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>65417000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>64204000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>49918000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>62277000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>62241000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>63014000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>64644000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>93681000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>90575600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>89116700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>61153000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>93051100</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4539,8 +4646,8 @@
       <c r="K48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -4593,68 +4700,71 @@
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>8</v>
+      <c r="AD48" s="3">
+        <v>0</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG48" s="3">
         <v>107000</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AJ48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK48" s="3">
         <v>112300</v>
       </c>
-      <c r="AK48" s="3" t="s">
+      <c r="AL48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4163000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3728000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3783000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3800000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3831000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3855000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3926000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3858000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3884000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>958000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>824000</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4670,8 +4780,8 @@
       <c r="S49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -4700,32 +4810,35 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>8</v>
+      <c r="AD49" s="3">
+        <v>0</v>
       </c>
       <c r="AE49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AF49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG49" s="3">
         <v>186000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>196000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>197800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>208000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>219500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>227300</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4831,8 +4944,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4938,115 +5054,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>109583000</v>
+      </c>
+      <c r="E52" s="3">
         <v>111896000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>113757000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>108741000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>108270000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>102687000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>95386000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>99117000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>94652000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2223000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1931000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1795000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1405000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>986000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>691000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>690000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>935000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>21889000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>21494000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>21249000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>20902000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>22953000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>401000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>576000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>864000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>21655000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1122000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>58102000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>59833000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1663700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1756900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2055700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>66368800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1128100</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5152,115 +5274,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>163950000</v>
+      </c>
+      <c r="E54" s="3">
         <v>163889000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>166933000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>161280000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>161631000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>157085000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>149265000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>154616000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>151208000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>146606000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>144048000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>147520000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>161806000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>171262000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>168417000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>168194000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>162861000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>180518000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>171466000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>166934000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>155732000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>168990000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>166850000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>165162000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>161985000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>155430000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>165036000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>162740000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>219824000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>222532000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>226643900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>219838800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>217025500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>214585000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>218622200</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5298,8 +5426,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5337,8 +5466,9 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5366,8 +5496,8 @@
       <c r="K57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -5444,43 +5574,46 @@
       <c r="AK57" s="3">
         <v>0</v>
       </c>
+      <c r="AL57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2551000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1743000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1765000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1610000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1613000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1122000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1192000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1444000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1471000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>141000</v>
       </c>
       <c r="M58" s="3">
         <v>141000</v>
       </c>
       <c r="N58" s="3">
-        <v>1000</v>
+        <v>141000</v>
       </c>
       <c r="O58" s="3">
         <v>1000</v>
@@ -5516,10 +5649,10 @@
         <v>1000</v>
       </c>
       <c r="Z58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA58" s="3">
         <v>97000</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>1000</v>
       </c>
       <c r="AB58" s="3">
         <v>1000</v>
@@ -5531,28 +5664,31 @@
         <v>1000</v>
       </c>
       <c r="AE58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
         <v>337000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>336600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>735900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>735500</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5580,116 +5716,119 @@
       <c r="K59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3">
         <v>81476000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>77358000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>81237000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>94232000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>101616000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>97995000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>98102000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>93872000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>90905000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>83454000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>80129000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>71002000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>83043000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>82049000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>81887000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>79627000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>71297000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>83034000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>80599000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>79668000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>79471000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>111603200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>105725300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>103261300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>67883100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>101627000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2551000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1743000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1765000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1610000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1613000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1122000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1192000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1444000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1471000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5765,222 +5904,231 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2374000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2567000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2441000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2015000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2025000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2451000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2448000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2485000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2461000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>2094000</v>
       </c>
       <c r="M61" s="3">
         <v>2094000</v>
       </c>
       <c r="N61" s="3">
+        <v>2094000</v>
+      </c>
+      <c r="O61" s="3">
         <v>2385000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2406000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2595000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2970000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>2969000</v>
       </c>
       <c r="S61" s="3">
         <v>2969000</v>
       </c>
       <c r="T61" s="3">
+        <v>2969000</v>
+      </c>
+      <c r="U61" s="3">
         <v>3044000</v>
-      </c>
-      <c r="U61" s="3">
-        <v>3043000</v>
       </c>
       <c r="V61" s="3">
         <v>3043000</v>
       </c>
       <c r="W61" s="3">
-        <v>3042000</v>
+        <v>3043000</v>
       </c>
       <c r="X61" s="3">
         <v>3042000</v>
       </c>
       <c r="Y61" s="3">
-        <v>3041000</v>
+        <v>3042000</v>
       </c>
       <c r="Z61" s="3">
         <v>3041000</v>
       </c>
       <c r="AA61" s="3">
-        <v>3136000</v>
+        <v>3041000</v>
       </c>
       <c r="AB61" s="3">
         <v>3136000</v>
       </c>
       <c r="AC61" s="3">
+        <v>3136000</v>
+      </c>
+      <c r="AD61" s="3">
         <v>3459000</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>3458000</v>
       </c>
       <c r="AE61" s="3">
         <v>3458000</v>
       </c>
       <c r="AF61" s="3">
+        <v>3458000</v>
+      </c>
+      <c r="AG61" s="3">
         <v>3123000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3122200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2726200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2725700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3550000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3548500</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>152664000</v>
+      </c>
+      <c r="E62" s="3">
         <v>153241000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>156145000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>151786000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>152122000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>147109000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>140666000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>145159000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>141589000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3">
         <v>196000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>205000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>213000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>226000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>274000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>304000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>333000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>18976000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>18607000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>18465000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>18414000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>18966000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>409000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>445000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>465000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>18454000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>516000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>527000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>56998000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>58827000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>542200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>636800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>656000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>60250000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>631400</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6086,8 +6234,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6193,8 +6344,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6300,115 +6454,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>157589000</v>
+      </c>
+      <c r="E66" s="3">
         <v>157882000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>160351000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>155411000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>155760000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>151032000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>144306000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>149088000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>145521000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>143257000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>139955000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>143004000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>155608000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>163009000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>160028000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>159832000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>154930000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>170408000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>161809000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>157386000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>148305000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>159651000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>156299000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>155098000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>152920000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>147217000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>156513000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>154280000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>210446000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>212523000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>212990900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>206486600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>204135100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>201590000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>203416200</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6446,8 +6606,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6553,8 +6714,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6660,8 +6824,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6767,8 +6934,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6874,115 +7044,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1052000</v>
+      </c>
+      <c r="E72" s="3">
         <v>954000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>907000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>855000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>697000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>505000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>302000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>40000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-118000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-201000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-994000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1201000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1269000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1310000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-3238000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3394000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3857000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-4957000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-5152000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-4833000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-4766000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-4718000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-11665000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-11785000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-12011000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-11732000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-11853000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-11995000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-12161000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-12719000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-9655600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-9804200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-9971400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-9742000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-9310300</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7088,8 +7264,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7195,8 +7374,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7302,115 +7484,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4383000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4005000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4719000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4043000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4153000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4193000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3127000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3697000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3954000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3349000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4093000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4516000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6198000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8253000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8389000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8362000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7931000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10110000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9657000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9548000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7427000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9339000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10551000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10064000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9065000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8213000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8523000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8460000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9378000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>10009000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>13653000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13352200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12890400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12995000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>15206000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7516,227 +7704,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>156000</v>
+      </c>
+      <c r="E81" s="3">
         <v>97000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>114000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>205000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>251000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>122000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>262000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>158000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>83000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>190000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>166000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>64000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>54000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>403000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>142000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>459000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1086000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>260000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-499000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-66000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-98000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-785000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>107000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>226000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>64000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>121000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>142000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>166000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>446000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>149000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>167000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-143000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-327000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7774,8 +7971,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7794,17 +7992,17 @@
       <c r="H83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3">
         <v>-22000</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -7881,8 +8079,11 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7988,8 +8189,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8095,8 +8299,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8202,8 +8409,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8309,8 +8519,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8416,115 +8629,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-179000</v>
+      </c>
+      <c r="E89" s="3">
         <v>79000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>719000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>316000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>231000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>364000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>403000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>715000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>156000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>219000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>418000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>296000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>419000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>140000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>121000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>747000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-936000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>421000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>788000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>508000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-76000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>459000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>302000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>418000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>131000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>234000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>580000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>653000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>401000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>456000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>570000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>605800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-49800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3591000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>819700</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8562,8 +8781,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8591,8 +8811,8 @@
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8651,26 +8871,29 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-9700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-10400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-66700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-25800</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8776,8 +8999,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8883,115 +9109,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>245000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-486000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-92000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1082000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>833000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>430000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>797000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>472000</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-372000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-403000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-578000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-600000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>181000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>670000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-636000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1825000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-139000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-811000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-374000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-954000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>117000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-44000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-333000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-36000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-149000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>236000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-145000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1581300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-892500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>190800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-3683000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1924000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9029,8 +9261,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9038,106 +9271,109 @@
         <v>43000</v>
       </c>
       <c r="E96" s="3">
+        <v>43000</v>
+      </c>
+      <c r="F96" s="3">
         <v>44000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>43000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>41000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>42000</v>
       </c>
       <c r="I96" s="3">
         <v>42000</v>
       </c>
       <c r="J96" s="3">
+        <v>42000</v>
+      </c>
+      <c r="K96" s="3">
         <v>23000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>20000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-20000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-22000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-20000</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-21000</v>
       </c>
       <c r="P96" s="3">
         <v>-21000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-19000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-20000</v>
       </c>
       <c r="S96" s="3">
         <v>-20000</v>
       </c>
       <c r="T96" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-18000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-58000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-19000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-20000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-1000</v>
       </c>
       <c r="AB96" s="3">
         <v>-1000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1700</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-1900</v>
       </c>
       <c r="AI96" s="3">
         <v>-1900</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9243,8 +9479,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9350,8 +9589,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9457,115 +9699,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-570000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-87000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>132000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-220000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1255000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-996000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1265000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-987000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-811000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-147000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-150000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>732000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-407000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-55000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>391000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-333000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-268000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>588000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1114000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-158000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>727000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>11000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>546000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-86000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-592000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-289000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-926000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-397000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-562400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>414200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>556600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-753400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>495400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>71300</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9593,8 +9841,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9671,111 +9919,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-504000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-31000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>365000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>58000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>201000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-432000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>525000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-183000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>72000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-104000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-143000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-391000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-493000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-88000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>595000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-534000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>373000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>77000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>211000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-160000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>96000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-106000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>449000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-505000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-251000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>255000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-422000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>240000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-251200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-600500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>269100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-612400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>398000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1033000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="92">
   <si>
     <t>VOYA</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="39" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1981000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1969000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2010000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1956000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2033000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2051000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1819000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1823000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1871000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1835000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1538000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1345000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1524000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1506000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1677000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2009000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2503000</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V8" s="3">
         <v>2231000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5505000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1719000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1705000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1844000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1878000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1972000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1848000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>837000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2259000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2114000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1981000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1281400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2185000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2192000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2059000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>8822000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2541200</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>859000</v>
+      </c>
+      <c r="E9" s="3">
         <v>897000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1043000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>993000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>899000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>907000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>861000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>856000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>739000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>810000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>83000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>60000</v>
-      </c>
-      <c r="O9" s="3">
-        <v>62000</v>
       </c>
       <c r="P9" s="3">
         <v>62000</v>
       </c>
       <c r="Q9" s="3">
+        <v>62000</v>
+      </c>
+      <c r="R9" s="3">
         <v>40000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>190000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>26000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>539000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>16000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>336000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>19000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>76000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>46000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>36000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>43000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>57000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>-27000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>86000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>74000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>100000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>-34400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>209000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>195000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>64000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>415000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1122000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1072000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>967000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>963000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1134000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1144000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>958000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>967000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1132000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1025000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1455000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1285000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1462000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1444000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1637000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1819000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2477000</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V10" s="3">
         <v>2215000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5169000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1700000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1629000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1798000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1842000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1929000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1791000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>864000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2173000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2040000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1881000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1315800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1976000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1997000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1995000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>8407000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2360500</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1155,8 +1167,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1265,8 +1278,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1375,103 +1391,106 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>3000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>70000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>12000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>80000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>15000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>10000</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>3000</v>
       </c>
       <c r="R14" s="3">
         <v>3000</v>
       </c>
       <c r="S14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="T14" s="3">
         <v>13000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>1000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>80000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>50000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>20000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>31000</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>3000</v>
       </c>
       <c r="AA14" s="3">
         <v>3000</v>
       </c>
       <c r="AB14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AC14" s="3">
         <v>26000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>6000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>7000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>14000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>15800</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>1000</v>
       </c>
       <c r="AI14" s="3">
         <v>1000</v>
@@ -1480,13 +1499,16 @@
         <v>1000</v>
       </c>
       <c r="AK14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AL14" s="3">
         <v>34000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1494,32 +1516,32 @@
         <v>25000</v>
       </c>
       <c r="E15" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F15" s="3">
         <v>26000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>24000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>23000</v>
       </c>
       <c r="H15" s="3">
         <v>23000</v>
       </c>
       <c r="I15" s="3">
+        <v>23000</v>
+      </c>
+      <c r="J15" s="3">
         <v>22000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>21000</v>
       </c>
       <c r="K15" s="3">
         <v>21000</v>
       </c>
       <c r="L15" s="3">
+        <v>21000</v>
+      </c>
+      <c r="M15" s="3">
         <v>9000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1595,8 +1617,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1632,228 +1657,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1730000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1729000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1812000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1771000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1659000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1707000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1567000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1575000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1502000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1644000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1407000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1231000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1326000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1338000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1308000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1548000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1424000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>-3049000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1682000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5510000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1711000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1618000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1716000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1670000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1671000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1699000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>667000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2018000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1811000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1905000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1000900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2078000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1965000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1883000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8422000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>251000</v>
+      </c>
+      <c r="E18" s="3">
         <v>240000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>198000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>185000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>374000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>344000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>252000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>248000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>369000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>191000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>131000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>114000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>198000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>168000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>369000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>461000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1079000</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V18" s="3">
         <v>549000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>8000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>87000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>128000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>208000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>301000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>149000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>170000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>241000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>303000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>76000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>280500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>107000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>227000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>176000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>400000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-283800</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1892,8 +1924,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1924,8 +1957,8 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1945,11 +1978,11 @@
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
@@ -2002,53 +2035,56 @@
       <c r="AL20" s="3">
         <v>0</v>
       </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>276000</v>
+      </c>
+      <c r="E21" s="3">
         <v>265000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>224000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>209000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>397000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>367000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>274000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>269000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>390000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>200000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>130000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3">
         <v>179000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2058,15 +2094,15 @@
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V21" s="3">
         <v>549000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-5000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2112,338 +2148,350 @@
       <c r="AL21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E22" s="3">
         <v>67000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>75000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>69000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>98000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>57000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>80000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>76000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>94000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>48000</v>
       </c>
       <c r="M22" s="3">
         <v>48000</v>
       </c>
       <c r="N22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="O22" s="3">
         <v>43000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>46000</v>
       </c>
       <c r="P22" s="3">
         <v>46000</v>
       </c>
       <c r="Q22" s="3">
+        <v>46000</v>
+      </c>
+      <c r="R22" s="3">
         <v>69000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>50000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>51000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>54000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>48000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>138000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>50000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>43000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>48000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>59000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>58000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>47000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>90000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>55000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>62000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>55000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>62300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>67000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>72000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>63000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>390000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>72100</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>188000</v>
+      </c>
+      <c r="E23" s="3">
         <v>173000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>120000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>116000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>276000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>287000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>102000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>172000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>263000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>141000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>83000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>71000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>152000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>122000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>300000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>411000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1028000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1038000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>501000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-143000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-42000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>44000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>80000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>149000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>243000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>102000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>80000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>186000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>241000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>21000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>218200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>40000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>155000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>113000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>10000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-355900</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E24" s="3">
         <v>22000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>18000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>41000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-17000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-74000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>28000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>12000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-54000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>29000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>11000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-202000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>40000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>112000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-48000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>55000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-72000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-264000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>33000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>9000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-41000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>21000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>45000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>42000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AI24" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3">
         <v>93000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-29000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-119400</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,228 +2600,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>161000</v>
+      </c>
+      <c r="E26" s="3">
         <v>151000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>121000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>98000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>235000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>288000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>119000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>246000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>235000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>129000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>137000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>42000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>143000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>111000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>502000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>371000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>916000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1086000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>446000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-71000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-48000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>50000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>344000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>144000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>210000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>93000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>121000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>165000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>196000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>17000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>176200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>80000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>155000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>20000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>39000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-236500</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E27" s="3">
         <v>139000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>93000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>98000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>201000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>234000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>118000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>248000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>154000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>69000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>190000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>166000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>64000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>54000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>398000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>143000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>465000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1072000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>318000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-136000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>27000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>30000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>334000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>111000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>184000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>84000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>57000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>142000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>138000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>17000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>94700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>15000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>103000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>19000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>10000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2882,8 +2939,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2927,73 +2987,76 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>5000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-1000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-6000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>14000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-58000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-363000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-93000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-128000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-1119000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>42000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>64000</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>28000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>429000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-3259000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>134000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>64000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-162000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-337000</v>
       </c>
-      <c r="AL29" s="3" t="s">
+      <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3102,8 +3165,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3212,8 +3278,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3244,8 +3313,8 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -3265,11 +3334,11 @@
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V32" s="3">
         <v>0</v>
@@ -3322,118 +3391,124 @@
       <c r="AL32" s="3">
         <v>0</v>
       </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E33" s="3">
         <v>156000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>97000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>114000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>205000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>251000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>122000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>262000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>158000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>83000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>190000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>166000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>64000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>54000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>403000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>142000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>459000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1086000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>260000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-499000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-66000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-98000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-785000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>107000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>226000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>64000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>121000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>142000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>166000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>446000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>149000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>167000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-143000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-327000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3542,233 +3617,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E35" s="3">
         <v>156000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>97000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>114000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>205000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>251000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>122000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>262000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>158000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>83000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>190000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>166000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>64000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>54000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>403000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>142000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>459000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1086000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>260000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-499000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-66000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-98000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-785000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>107000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>226000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>64000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>121000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>142000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>166000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>446000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>149000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>167000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-143000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-327000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3807,8 +3891,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3847,151 +3932,155 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1179000</v>
+      </c>
+      <c r="E41" s="3">
         <v>868000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1399000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1457000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1066000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>995000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>937000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>829000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1195000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>724000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1007000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>935000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1039000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1125000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1573000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1818000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1850000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1316000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1723000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1136000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1149000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1085000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1249000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1450000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1541000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1340000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1568000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1885000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1620000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1597000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1435000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2072900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2713300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2531300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2229000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2951600</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>366000</v>
+      </c>
+      <c r="E42" s="3">
         <v>357000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>340000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>298000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>367000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>506000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>483000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>704000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>423000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>309000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4067,59 +4156,62 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>314000</v>
+      </c>
+      <c r="E43" s="3">
         <v>334000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>338000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>323000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>300000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>335000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>322000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N43" s="3">
         <v>12426000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13561000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13079000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13261000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13635000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13580000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4132,8 +4224,8 @@
       <c r="W43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -4177,8 +4269,11 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4209,8 +4304,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4287,41 +4382,44 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12556000</v>
+      </c>
+      <c r="E45" s="3">
         <v>12809000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12917000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13298000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13160000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13476000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13647000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13296000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13899000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14330000</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -4397,41 +4495,44 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14415000</v>
+      </c>
+      <c r="E46" s="3">
         <v>14368000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14994000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15376000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14893000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15312000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15389000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14810000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15479000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15328000</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4507,118 +4608,124 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>27906000</v>
+      </c>
+      <c r="E47" s="3">
         <v>27883000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>26015000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>26895000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>26353000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>26599000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>27352000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>27003000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>28304000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>29534000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>38086000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>38408000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>39911000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>41978000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>44387000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>47491000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>45341000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>44660000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>54841000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>54357000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>54264000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>51772000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>52700000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>67153000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>65417000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>64204000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>49918000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>62277000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>62241000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>63014000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>64644000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>93681000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>90575600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>89116700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>61153000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>93051100</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4649,8 +4756,8 @@
       <c r="L48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -4703,71 +4810,74 @@
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>8</v>
+      <c r="AE48" s="3">
+        <v>0</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH48" s="3">
         <v>107000</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AK48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL48" s="3">
         <v>112300</v>
       </c>
-      <c r="AL48" s="3" t="s">
+      <c r="AM48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4115000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4163000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3728000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3783000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3800000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3831000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3855000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3926000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3858000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3884000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>958000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>824000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4783,8 +4893,8 @@
       <c r="T49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -4813,32 +4923,35 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>8</v>
+      <c r="AE49" s="3">
+        <v>0</v>
       </c>
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AG49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH49" s="3">
         <v>186000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>196000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>197800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>208000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>219500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>227300</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4947,8 +5060,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5057,118 +5173,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>118178000</v>
+      </c>
+      <c r="E52" s="3">
         <v>109583000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>111896000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>113757000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>108741000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>108270000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>102687000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>95386000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>99117000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>94652000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2223000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1931000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1795000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1405000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>986000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>691000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>690000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>935000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>21889000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>21494000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>21249000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>20902000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>22953000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>401000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>576000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>864000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>21655000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1122000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>58102000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>59833000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1663700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1756900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2055700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>66368800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1128100</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5277,118 +5399,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>172436000</v>
+      </c>
+      <c r="E54" s="3">
         <v>163950000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>163889000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>166933000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>161280000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>161631000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>157085000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>149265000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>154616000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>151208000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>146606000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>144048000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>147520000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>161806000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>171262000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>168417000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>168194000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>162861000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>180518000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>171466000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>166934000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>155732000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>168990000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>166850000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>165162000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>161985000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>155430000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>165036000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>162740000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>219824000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>222532000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>226643900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>219838800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>217025500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>214585000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>218622200</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5427,8 +5555,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5467,8 +5596,9 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5499,8 +5629,8 @@
       <c r="L57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -5577,46 +5707,49 @@
       <c r="AL57" s="3">
         <v>0</v>
       </c>
+      <c r="AM57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2908000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2551000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1743000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1765000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1610000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1613000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1122000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1192000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1444000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1471000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>141000</v>
       </c>
       <c r="N58" s="3">
         <v>141000</v>
       </c>
       <c r="O58" s="3">
-        <v>1000</v>
+        <v>141000</v>
       </c>
       <c r="P58" s="3">
         <v>1000</v>
@@ -5652,10 +5785,10 @@
         <v>1000</v>
       </c>
       <c r="AA58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB58" s="3">
         <v>97000</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>1000</v>
       </c>
       <c r="AC58" s="3">
         <v>1000</v>
@@ -5667,28 +5800,31 @@
         <v>1000</v>
       </c>
       <c r="AF58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
         <v>337000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>336600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>735900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>735500</v>
       </c>
-      <c r="AK58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5719,119 +5855,122 @@
       <c r="L59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3">
         <v>81476000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>77358000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>81237000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>94232000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>101616000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>97995000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>98102000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>93872000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>90905000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>83454000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>80129000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>71002000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>83043000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>82049000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>81887000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>79627000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>71297000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>83034000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>80599000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>79668000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>79471000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>111603200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>105725300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>103261300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>67883100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>101627000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2908000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2551000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1743000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1765000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1610000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1613000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1122000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1192000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1444000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1471000</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5907,228 +6046,237 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1928000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2374000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2567000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2441000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2015000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2025000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2451000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2448000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2485000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2461000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>2094000</v>
       </c>
       <c r="N61" s="3">
         <v>2094000</v>
       </c>
       <c r="O61" s="3">
+        <v>2094000</v>
+      </c>
+      <c r="P61" s="3">
         <v>2385000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2406000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2595000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2970000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>2969000</v>
       </c>
       <c r="T61" s="3">
         <v>2969000</v>
       </c>
       <c r="U61" s="3">
+        <v>2969000</v>
+      </c>
+      <c r="V61" s="3">
         <v>3044000</v>
-      </c>
-      <c r="V61" s="3">
-        <v>3043000</v>
       </c>
       <c r="W61" s="3">
         <v>3043000</v>
       </c>
       <c r="X61" s="3">
-        <v>3042000</v>
+        <v>3043000</v>
       </c>
       <c r="Y61" s="3">
         <v>3042000</v>
       </c>
       <c r="Z61" s="3">
-        <v>3041000</v>
+        <v>3042000</v>
       </c>
       <c r="AA61" s="3">
         <v>3041000</v>
       </c>
       <c r="AB61" s="3">
-        <v>3136000</v>
+        <v>3041000</v>
       </c>
       <c r="AC61" s="3">
         <v>3136000</v>
       </c>
       <c r="AD61" s="3">
+        <v>3136000</v>
+      </c>
+      <c r="AE61" s="3">
         <v>3459000</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>3458000</v>
       </c>
       <c r="AF61" s="3">
         <v>3458000</v>
       </c>
       <c r="AG61" s="3">
+        <v>3458000</v>
+      </c>
+      <c r="AH61" s="3">
         <v>3123000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3122200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2726200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2725700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3550000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3548500</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>161047000</v>
+      </c>
+      <c r="E62" s="3">
         <v>152664000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>153241000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>156145000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>151786000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>152122000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>147109000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>140666000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>145159000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>141589000</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O62" s="3">
         <v>196000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>205000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>213000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>226000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>274000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>304000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>333000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>18976000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>18607000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>18465000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>18414000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>18966000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>409000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>445000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>465000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>18454000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>516000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>527000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>56998000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>58827000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>542200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>636800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>656000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>60250000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>631400</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6237,8 +6385,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6347,8 +6498,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6457,118 +6611,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>165883000</v>
+      </c>
+      <c r="E66" s="3">
         <v>157589000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>157882000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>160351000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>155411000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>155760000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>151032000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>144306000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>149088000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>145521000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>143257000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>139955000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>143004000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>155608000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>163009000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>160028000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>159832000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>154930000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>170408000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>161809000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>157386000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>148305000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>159651000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>156299000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>155098000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>152920000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>147217000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>156513000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>154280000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>210446000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>212523000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>212990900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>206486600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>204135100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>201590000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>203416200</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6607,8 +6767,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6717,8 +6878,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6827,8 +6991,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6937,8 +7104,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7047,118 +7217,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1170000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1052000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>954000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>907000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>855000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>697000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>505000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>302000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>40000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-118000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-201000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-994000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1201000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1269000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1310000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-3238000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-3394000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-3857000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-4957000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-5152000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-4833000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-4766000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-4718000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-11665000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-11785000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-12011000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-11732000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-11853000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-11995000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-12161000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-12719000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-9655600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-9804200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-9971400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-9742000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-9310300</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7267,8 +7443,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7377,8 +7556,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7487,118 +7669,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4629000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4383000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4005000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4719000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4043000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4153000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4193000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3127000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3697000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3954000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3349000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4093000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4516000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6198000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8253000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8389000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8362000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7931000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10110000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9657000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9548000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7427000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9339000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>10551000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>10064000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9065000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8213000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8523000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8460000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>9378000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>10009000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13653000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>13352200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12890400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12995000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>15206000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7707,233 +7895,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E81" s="3">
         <v>156000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>97000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>114000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>205000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>251000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>122000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>262000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>158000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>83000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>190000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>166000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>64000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>54000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>403000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>142000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>459000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1086000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>260000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-499000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-66000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-98000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-785000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>107000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>226000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>64000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>121000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>142000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>166000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>446000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>149000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>167000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-143000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-327000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7972,8 +8169,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7995,17 +8193,17 @@
       <c r="I83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
         <v>-22000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -8082,8 +8280,11 @@
       <c r="AL83" s="3">
         <v>0</v>
       </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8192,8 +8393,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8302,8 +8506,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8412,8 +8619,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8522,8 +8732,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8632,118 +8845,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>742000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-179000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>79000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>719000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>316000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>231000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>364000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>403000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>715000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>156000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>219000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>418000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>296000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>419000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>140000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>121000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>747000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-936000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>421000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>788000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>508000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-76000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>459000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>302000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>418000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>131000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>234000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>580000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>653000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>401000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>456000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>570000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>605800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-49800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3591000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>819700</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8782,8 +9001,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8814,8 +9034,8 @@
       <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8874,26 +9094,29 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH91" s="3">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-9700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-10400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-66700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-25800</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9002,8 +9225,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9112,118 +9338,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-524000</v>
+      </c>
+      <c r="E94" s="3">
         <v>245000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-23000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-486000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-92000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1082000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>833000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>430000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>797000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>472000</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-372000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-403000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-578000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-600000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>181000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>670000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-636000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1825000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-139000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-811000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-374000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-954000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>117000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-44000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-333000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-36000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-149000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>236000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-145000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1581300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-892500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>190800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3683000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1924000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9262,118 +9494,122 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>43000</v>
+        <v>47000</v>
       </c>
       <c r="E96" s="3">
         <v>43000</v>
       </c>
       <c r="F96" s="3">
+        <v>43000</v>
+      </c>
+      <c r="G96" s="3">
         <v>44000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>43000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>41000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>42000</v>
       </c>
       <c r="J96" s="3">
         <v>42000</v>
       </c>
       <c r="K96" s="3">
+        <v>42000</v>
+      </c>
+      <c r="L96" s="3">
         <v>23000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>20000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-20000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-22000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-20000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-21000</v>
       </c>
       <c r="Q96" s="3">
         <v>-21000</v>
       </c>
       <c r="R96" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-19000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-20000</v>
       </c>
       <c r="T96" s="3">
         <v>-20000</v>
       </c>
       <c r="U96" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-18000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-58000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-19000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-20000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-1000</v>
       </c>
       <c r="AC96" s="3">
         <v>-1000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1700</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-1900</v>
       </c>
       <c r="AJ96" s="3">
         <v>-1900</v>
       </c>
       <c r="AK96" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9482,8 +9718,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9592,8 +9831,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9702,118 +9944,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-570000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-87000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>132000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-220000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1255000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-996000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1265000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-987000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-811000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-147000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-150000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>732000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-407000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-55000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>391000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-333000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-268000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>588000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1114000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-158000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>727000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>11000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>546000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-86000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-592000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-289000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-926000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-397000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-562400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>414200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>556600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-753400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>495400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>71300</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9844,8 +10092,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9922,114 +10170,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>311000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-504000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-31000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>365000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>58000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>201000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-432000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>525000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-183000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>72000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-104000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-143000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-391000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-493000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-88000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>595000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-534000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>373000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>77000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>211000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-160000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>96000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-106000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>449000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-505000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-251000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>255000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-422000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>240000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-251200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-600500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>269100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-612400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>398000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-1033000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="92">
   <si>
     <t>VOYA</t>
   </si>
@@ -656,491 +656,503 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="40" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2111000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2128000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1981000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1969000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2010000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1956000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2033000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2051000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1819000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1823000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1871000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1835000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1538000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1345000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1524000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1506000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1677000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2009000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2503000</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X8" s="3">
         <v>2231000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5505000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1719000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1705000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1844000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1878000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1972000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1848000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>837000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2259000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2114000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1981000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1281400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2185000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2192000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2059000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>8822000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2541200</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>939000</v>
+      </c>
+      <c r="E9" s="3">
         <v>915000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>859000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>897000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1043000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>993000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>899000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>907000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>861000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>856000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>739000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>810000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>83000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>60000</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>62000</v>
       </c>
       <c r="R9" s="3">
         <v>62000</v>
       </c>
       <c r="S9" s="3">
+        <v>62000</v>
+      </c>
+      <c r="T9" s="3">
         <v>40000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>190000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>26000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>539000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>16000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>336000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>19000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>76000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>46000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>36000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>43000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>57000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>-27000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>86000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>74000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>100000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>-34400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>209000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>195000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>64000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>415000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1172000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1213000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1122000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1072000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>967000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>963000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1134000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1144000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>958000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>967000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1132000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1025000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1455000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1285000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1462000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1444000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1637000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1819000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2477000</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X10" s="3">
         <v>2215000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5169000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1700000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1629000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1798000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1842000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1929000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1791000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>864000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2173000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2040000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1881000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1315800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1976000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1997000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1995000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>8407000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>2360500</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,8 +1193,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1297,8 +1310,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1413,8 +1429,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1427,8 +1446,8 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>3000</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1439,83 +1458,83 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>70000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>12000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>80000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>15000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>10000</v>
-      </c>
-      <c r="S14" s="3">
-        <v>3000</v>
       </c>
       <c r="T14" s="3">
         <v>3000</v>
       </c>
       <c r="U14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="V14" s="3">
         <v>13000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>1000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>80000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>50000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>20000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>31000</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>3000</v>
       </c>
       <c r="AC14" s="3">
         <v>3000</v>
       </c>
       <c r="AD14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AE14" s="3">
         <v>26000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>6000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>7000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>14000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>15800</v>
-      </c>
-      <c r="AJ14" s="3">
-        <v>1000</v>
       </c>
       <c r="AK14" s="3">
         <v>1000</v>
@@ -1524,52 +1543,55 @@
         <v>1000</v>
       </c>
       <c r="AM14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AN14" s="3">
         <v>34000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E15" s="3">
         <v>26000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>25000</v>
       </c>
       <c r="F15" s="3">
         <v>25000</v>
       </c>
       <c r="G15" s="3">
+        <v>25000</v>
+      </c>
+      <c r="H15" s="3">
         <v>26000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>24000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>23000</v>
       </c>
       <c r="J15" s="3">
         <v>23000</v>
       </c>
       <c r="K15" s="3">
+        <v>23000</v>
+      </c>
+      <c r="L15" s="3">
         <v>22000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>21000</v>
       </c>
       <c r="M15" s="3">
         <v>21000</v>
       </c>
       <c r="N15" s="3">
+        <v>21000</v>
+      </c>
+      <c r="O15" s="3">
         <v>9000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1645,8 +1667,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,240 +1709,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1885000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1761000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1730000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1729000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1812000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1815000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1771000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1659000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1707000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1567000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1575000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1502000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1644000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1407000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1231000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1326000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1338000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1308000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1548000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1424000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-3049000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1682000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5510000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1711000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1618000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1716000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1670000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1671000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1699000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>667000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2018000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1811000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1905000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1000900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2078000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1965000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1883000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8422000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>226000</v>
+      </c>
+      <c r="E18" s="3">
         <v>367000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>251000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>240000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>195000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>185000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>374000</v>
+      </c>
+      <c r="K18" s="3">
+        <v>344000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>252000</v>
+      </c>
+      <c r="M18" s="3">
+        <v>248000</v>
+      </c>
+      <c r="N18" s="3">
+        <v>369000</v>
+      </c>
+      <c r="O18" s="3">
+        <v>191000</v>
+      </c>
+      <c r="P18" s="3">
+        <v>131000</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>114000</v>
+      </c>
+      <c r="R18" s="3">
         <v>198000</v>
       </c>
-      <c r="H18" s="3">
-        <v>185000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>374000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>344000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>252000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>248000</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="S18" s="3">
+        <v>168000</v>
+      </c>
+      <c r="T18" s="3">
         <v>369000</v>
       </c>
-      <c r="N18" s="3">
-        <v>191000</v>
-      </c>
-      <c r="O18" s="3">
-        <v>131000</v>
-      </c>
-      <c r="P18" s="3">
-        <v>114000</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>198000</v>
-      </c>
-      <c r="R18" s="3">
-        <v>168000</v>
-      </c>
-      <c r="S18" s="3">
-        <v>369000</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>461000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1079000</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X18" s="3">
         <v>549000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>8000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>87000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>128000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>208000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>301000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>149000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>170000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>241000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>303000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>76000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>280500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>107000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>227000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>176000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>400000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>-283800</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1958,8 +1990,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1996,8 +2029,8 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -2017,11 +2050,11 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W20" s="3">
-        <v>0</v>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X20" s="3">
         <v>0</v>
@@ -2074,59 +2107,62 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>253000</v>
+      </c>
+      <c r="E21" s="3">
         <v>393000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>276000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>265000</v>
       </c>
-      <c r="G21" s="3">
-        <v>224000</v>
-      </c>
       <c r="H21" s="3">
+        <v>221000</v>
+      </c>
+      <c r="I21" s="3">
         <v>209000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>397000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>367000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>274000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>269000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>390000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>200000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>130000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3">
         <v>179000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2136,15 +2172,15 @@
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X21" s="3">
         <v>549000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2190,356 +2226,368 @@
       <c r="AN21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E22" s="3">
         <v>60000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>63000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>67000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>75000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>69000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>98000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>57000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>80000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>76000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>94000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>48000</v>
       </c>
       <c r="O22" s="3">
         <v>48000</v>
       </c>
       <c r="P22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="Q22" s="3">
         <v>43000</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>46000</v>
       </c>
       <c r="R22" s="3">
         <v>46000</v>
       </c>
       <c r="S22" s="3">
+        <v>46000</v>
+      </c>
+      <c r="T22" s="3">
         <v>69000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>50000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>51000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>54000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>48000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>138000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>50000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>43000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>48000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>59000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>58000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>47000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>90000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>55000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>62000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>55000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>62300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>67000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>72000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>63000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>390000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>72100</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>169000</v>
+      </c>
+      <c r="E23" s="3">
         <v>307000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>188000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>173000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>120000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>116000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>276000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>287000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>102000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>172000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>263000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>141000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>83000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>71000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>152000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>122000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>300000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>411000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1028000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1038000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>501000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-143000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-42000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>44000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>80000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>149000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>243000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>102000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>80000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>186000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>241000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>21000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>218200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>40000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>155000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>113000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>10000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-355900</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E24" s="3">
         <v>35000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>27000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>22000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>18000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>41000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-17000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-74000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>28000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>12000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-54000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>29000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>11000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-202000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>40000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>112000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-48000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>55000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-72000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-264000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>33000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>9000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-41000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>21000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>45000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>42000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AK24" s="3">
-        <v>0</v>
-      </c>
       <c r="AL24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="3">
         <v>93000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-29000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-119400</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2654,240 +2702,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E26" s="3">
         <v>272000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>161000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>151000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>121000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>98000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>235000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>288000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>119000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>246000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>235000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>129000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>137000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>42000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>143000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>111000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>502000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>371000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>916000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1086000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>446000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-71000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-48000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>50000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>344000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>144000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>210000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>93000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>121000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>165000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>196000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>17000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>176200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>80000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>155000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>20000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>39000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-236500</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E27" s="3">
         <v>176000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>162000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>139000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>93000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>98000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>201000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>234000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>118000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>248000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>154000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>69000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>190000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>166000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>64000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>54000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>398000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>143000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>465000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1072000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>318000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-136000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>27000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>30000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>334000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>111000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>184000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>84000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>57000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>142000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>138000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>17000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>94700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>15000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>103000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>19000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>10000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3002,8 +3059,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3053,73 +3113,76 @@
         <v>0</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>5000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-1000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-6000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>14000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-58000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-363000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-93000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-128000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-1119000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>42000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-20000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>64000</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>28000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>429000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-3259000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>134000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>64000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-162000</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>-337000</v>
       </c>
-      <c r="AN29" s="3" t="s">
+      <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3234,8 +3297,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3350,8 +3416,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3388,8 +3457,8 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -3409,11 +3478,11 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W32" s="3">
-        <v>0</v>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X32" s="3">
         <v>0</v>
@@ -3466,124 +3535,130 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E33" s="3">
         <v>192000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>166000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>156000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>97000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>114000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>205000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>251000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>122000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>262000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>158000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>83000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>190000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>166000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>64000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>54000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>403000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>142000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>459000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1086000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>260000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-499000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-66000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-98000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-785000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>107000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>226000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>64000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>121000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>142000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>166000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>446000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>149000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>167000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-143000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-327000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3698,245 +3773,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E35" s="3">
         <v>192000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>166000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>156000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>97000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>114000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>205000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>251000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>122000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>262000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>158000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>83000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>190000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>166000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>64000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>54000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>403000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>142000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>459000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1086000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>260000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-499000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-66000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-98000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-785000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>107000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>226000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>64000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>121000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>142000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>166000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>446000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>149000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>167000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-143000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-327000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3977,8 +4061,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4019,163 +4104,167 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1228000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1157000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1179000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>868000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1399000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1457000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1066000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>995000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>937000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>829000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1195000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>724000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1007000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>935000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1039000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1125000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1573000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1818000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1850000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1316000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1723000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1136000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1149000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1085000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1249000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1450000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1541000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1340000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1568000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1885000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1620000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1597000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1435000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2072900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2713300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2531300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2229000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2951600</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>329000</v>
+      </c>
+      <c r="E42" s="3">
         <v>345000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>366000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>357000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>340000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>298000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>367000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>506000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>483000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>704000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>423000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>309000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4251,65 +4340,68 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>346000</v>
+      </c>
+      <c r="E43" s="3">
         <v>331000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>314000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>334000</v>
       </c>
-      <c r="G43" s="3">
-        <v>338000</v>
-      </c>
       <c r="H43" s="3">
+        <v>350000</v>
+      </c>
+      <c r="I43" s="3">
         <v>323000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>300000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>335000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>322000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P43" s="3">
         <v>12426000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13561000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13079000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13261000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13635000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>13580000</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4322,8 +4414,8 @@
       <c r="Y43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
+      <c r="Z43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
@@ -4367,8 +4459,11 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4405,8 +4500,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4483,47 +4578,50 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12284000</v>
+      </c>
+      <c r="E45" s="3">
         <v>12417000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12556000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12809000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12917000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13298000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13160000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13476000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13647000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13296000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13899000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14330000</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -4599,47 +4697,50 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14351000</v>
+      </c>
+      <c r="E46" s="3">
         <v>14250000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14415000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14368000</v>
       </c>
-      <c r="G46" s="3">
-        <v>14994000</v>
-      </c>
       <c r="H46" s="3">
+        <v>15198000</v>
+      </c>
+      <c r="I46" s="3">
         <v>15376000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14893000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15312000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15389000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14810000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15479000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15328000</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4715,124 +4816,130 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>28518000</v>
+      </c>
+      <c r="E47" s="3">
         <v>28398000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>27906000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>27883000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>26015000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>26895000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>26353000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>26599000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>27352000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>27003000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>28304000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>29534000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>38086000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>38408000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>39911000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>41978000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>44387000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>47491000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>45341000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>44660000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>54841000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>54357000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>54264000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>51772000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>52700000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>67153000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>65417000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>64204000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>49918000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>62277000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>62241000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>63014000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>64644000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>93681000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>90575600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>89116700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>61153000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>93051100</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4869,8 +4976,8 @@
       <c r="N48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -4923,77 +5030,80 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>8</v>
+      <c r="AG48" s="3">
+        <v>0</v>
       </c>
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>107000</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AM48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN48" s="3">
         <v>112300</v>
       </c>
-      <c r="AN48" s="3" t="s">
+      <c r="AO48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4079000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4076000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4115000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4163000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3728000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3783000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3800000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3831000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3855000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3926000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3858000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3884000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>958000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>824000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>8</v>
       </c>
@@ -5009,8 +5119,8 @@
       <c r="V49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -5039,32 +5149,35 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>8</v>
+      <c r="AG49" s="3">
+        <v>0</v>
       </c>
       <c r="AH49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>186000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>196000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>197800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>208000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>219500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>227300</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5179,8 +5292,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5295,124 +5411,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>124031000</v>
+      </c>
+      <c r="E52" s="3">
         <v>123132000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>118178000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>109583000</v>
       </c>
-      <c r="G52" s="3">
-        <v>111896000</v>
-      </c>
       <c r="H52" s="3">
+        <v>111692000</v>
+      </c>
+      <c r="I52" s="3">
         <v>113757000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>108741000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>108270000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>102687000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>95386000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>99117000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>94652000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2223000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1931000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1795000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1405000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>986000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>691000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>690000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>935000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>21889000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>21494000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>21249000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>20902000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>22953000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>401000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>576000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>864000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>21655000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1122000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>58102000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>59833000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1663700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1756900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2055700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>66368800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1128100</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5527,124 +5649,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>178859000</v>
+      </c>
+      <c r="E54" s="3">
         <v>177448000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>172436000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>163950000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>163889000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>166933000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>161280000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>161631000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>157085000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>149265000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>154616000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>151208000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>146606000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>144048000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>147520000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>161806000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>171262000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>168417000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>168194000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>162861000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>180518000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>171466000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>166934000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>155732000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>168990000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>166850000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>165162000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>161985000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>155430000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>165036000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>162740000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>219824000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>222532000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>226643900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>219838800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>217025500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>214585000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>218622200</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5685,8 +5813,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5727,8 +5856,9 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5765,8 +5895,8 @@
       <c r="N57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
+      <c r="O57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
@@ -5843,52 +5973,55 @@
       <c r="AN57" s="3">
         <v>0</v>
       </c>
+      <c r="AO57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2923000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2979000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2908000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2551000</v>
       </c>
-      <c r="G58" s="3">
-        <v>2896000</v>
-      </c>
       <c r="H58" s="3">
+        <v>2861000</v>
+      </c>
+      <c r="I58" s="3">
         <v>1765000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1610000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1613000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1122000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1192000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1444000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1471000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>141000</v>
       </c>
       <c r="P58" s="3">
         <v>141000</v>
       </c>
       <c r="Q58" s="3">
-        <v>1000</v>
+        <v>141000</v>
       </c>
       <c r="R58" s="3">
         <v>1000</v>
@@ -5924,10 +6057,10 @@
         <v>1000</v>
       </c>
       <c r="AC58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AD58" s="3">
         <v>97000</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>1000</v>
       </c>
       <c r="AE58" s="3">
         <v>1000</v>
@@ -5939,28 +6072,31 @@
         <v>1000</v>
       </c>
       <c r="AH58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>337000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>336600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>735900</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>735500</v>
       </c>
-      <c r="AM58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AN58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5997,125 +6133,128 @@
       <c r="N59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P59" s="3">
         <v>81476000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>77358000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>81237000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>94232000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>101616000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>97995000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>98102000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>93872000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>90905000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>83454000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>80129000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>71002000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>83043000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>82049000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>81887000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>79627000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>71297000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>83034000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>80599000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>79668000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>79471000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>111603200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>105725300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>103261300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>67883100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>101627000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2923000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2979000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2908000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2551000</v>
       </c>
-      <c r="G60" s="3">
-        <v>2896000</v>
-      </c>
       <c r="H60" s="3">
+        <v>2861000</v>
+      </c>
+      <c r="I60" s="3">
         <v>1765000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1610000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1613000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1122000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1192000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1444000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1471000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6191,240 +6330,249 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1927000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1783000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1928000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2374000</v>
       </c>
-      <c r="G61" s="3">
-        <v>2567000</v>
-      </c>
       <c r="H61" s="3">
+        <v>2416000</v>
+      </c>
+      <c r="I61" s="3">
         <v>2441000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2015000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2025000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2451000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2448000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2485000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2461000</v>
-      </c>
-      <c r="O61" s="3">
-        <v>2094000</v>
       </c>
       <c r="P61" s="3">
         <v>2094000</v>
       </c>
       <c r="Q61" s="3">
+        <v>2094000</v>
+      </c>
+      <c r="R61" s="3">
         <v>2385000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2406000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2595000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2970000</v>
-      </c>
-      <c r="U61" s="3">
-        <v>2969000</v>
       </c>
       <c r="V61" s="3">
         <v>2969000</v>
       </c>
       <c r="W61" s="3">
+        <v>2969000</v>
+      </c>
+      <c r="X61" s="3">
         <v>3044000</v>
-      </c>
-      <c r="X61" s="3">
-        <v>3043000</v>
       </c>
       <c r="Y61" s="3">
         <v>3043000</v>
       </c>
       <c r="Z61" s="3">
-        <v>3042000</v>
+        <v>3043000</v>
       </c>
       <c r="AA61" s="3">
         <v>3042000</v>
       </c>
       <c r="AB61" s="3">
-        <v>3041000</v>
+        <v>3042000</v>
       </c>
       <c r="AC61" s="3">
         <v>3041000</v>
       </c>
       <c r="AD61" s="3">
-        <v>3136000</v>
+        <v>3041000</v>
       </c>
       <c r="AE61" s="3">
         <v>3136000</v>
       </c>
       <c r="AF61" s="3">
+        <v>3136000</v>
+      </c>
+      <c r="AG61" s="3">
         <v>3459000</v>
-      </c>
-      <c r="AG61" s="3">
-        <v>3458000</v>
       </c>
       <c r="AH61" s="3">
         <v>3458000</v>
       </c>
       <c r="AI61" s="3">
+        <v>3458000</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>3123000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3122200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2726200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2725700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3550000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3548500</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>166636000</v>
+      </c>
+      <c r="E62" s="3">
         <v>165603000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>161047000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>152664000</v>
       </c>
-      <c r="G62" s="3">
-        <v>152088000</v>
-      </c>
       <c r="H62" s="3">
+        <v>152274000</v>
+      </c>
+      <c r="I62" s="3">
         <v>156145000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>151786000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>152122000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>147109000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>140666000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>145159000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>141589000</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62" s="3">
         <v>196000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>205000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>213000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>226000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>274000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>304000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>333000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>18976000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>18607000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>18465000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>18414000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>18966000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>409000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>445000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>465000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>18454000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>516000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>527000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>56998000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>58827000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>542200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>636800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>656000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>60250000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>631400</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6539,8 +6687,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6655,8 +6806,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6771,124 +6925,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>171820000</v>
+      </c>
+      <c r="E66" s="3">
         <v>170365000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>165883000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>157589000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>157882000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>160351000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>155411000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>155760000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>151032000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>144306000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>149088000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>145521000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>143257000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>139955000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>143004000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>155608000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>163009000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>160028000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>159832000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>154930000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>170408000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>161809000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>157386000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>148305000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>159651000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>156299000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>155098000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>152920000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>147217000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>156513000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>154280000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>210446000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>212523000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>212990900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>206486600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>204135100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>201590000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>203416200</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6929,8 +7089,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7045,8 +7206,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7161,8 +7325,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7277,8 +7444,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7393,124 +7563,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1392000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1301000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1170000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1052000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>954000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>907000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>855000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>697000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>505000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>302000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>40000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-118000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-201000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-994000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1201000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1269000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1310000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-3238000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3394000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3857000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-4957000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5152000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-4833000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-4766000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-4718000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-11665000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-11785000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-12011000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-11732000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-11853000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-11995000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-12161000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-12719000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-9655600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-9804200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-9971400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-9742000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-9310300</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7625,8 +7801,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7741,8 +7920,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7857,124 +8039,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4953000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4957000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4629000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4383000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4005000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4719000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4043000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4153000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4193000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3127000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3697000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3954000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3349000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4093000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4516000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6198000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8253000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8389000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8362000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7931000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10110000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9657000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9548000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7427000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9339000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>10551000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10064000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9065000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8213000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8523000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8460000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>9378000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>10009000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>13653000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>13352200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>12890400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>12995000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>15206000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8089,245 +8277,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E81" s="3">
         <v>192000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>166000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>156000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>97000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>114000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>205000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>251000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>122000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>262000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>158000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>83000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>190000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>166000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>64000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>54000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>403000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>142000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>459000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1086000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>260000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-499000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-66000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-98000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-785000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>107000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>226000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>64000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>121000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>142000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>166000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>446000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>149000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>167000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-143000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-327000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8368,8 +8565,9 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8397,17 +8595,17 @@
       <c r="K83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M83" s="3">
         <v>-22000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -8484,8 +8682,11 @@
       <c r="AN83" s="3">
         <v>0</v>
       </c>
+      <c r="AO83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8600,8 +8801,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8716,8 +8920,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8832,8 +9039,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8948,8 +9158,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9064,124 +9277,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>557000</v>
+      </c>
+      <c r="E89" s="3">
         <v>168000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>742000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-179000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>79000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>719000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>316000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>231000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>364000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>403000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>715000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>156000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>219000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>418000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>296000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>419000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>140000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>121000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>747000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-936000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>421000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>788000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>508000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-76000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>459000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>302000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>418000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>131000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>234000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>580000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>653000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>401000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>456000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>570000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>605800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-49800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>3591000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>819700</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9222,8 +9441,9 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9260,8 +9480,8 @@
       <c r="N91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -9320,26 +9540,29 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ91" s="3">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-9700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-10400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-66700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-25800</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9454,8 +9677,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9570,124 +9796,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-372000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-718000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-524000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>245000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-23000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-486000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-92000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1082000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>833000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>430000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>797000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>472000</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-372000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-403000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-578000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-600000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>181000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>670000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-636000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1825000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-139000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-811000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-374000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-954000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>117000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-44000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-333000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-36000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-149000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>236000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-145000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1581300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-892500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>190800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-3683000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1924000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9728,124 +9960,128 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E96" s="3">
         <v>43000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>47000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>43000</v>
       </c>
       <c r="G96" s="3">
         <v>43000</v>
       </c>
       <c r="H96" s="3">
+        <v>43000</v>
+      </c>
+      <c r="I96" s="3">
         <v>44000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>43000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>41000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>42000</v>
       </c>
       <c r="L96" s="3">
         <v>42000</v>
       </c>
       <c r="M96" s="3">
+        <v>42000</v>
+      </c>
+      <c r="N96" s="3">
         <v>23000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>20000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-20000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-20000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-21000</v>
       </c>
       <c r="S96" s="3">
         <v>-21000</v>
       </c>
       <c r="T96" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-19000</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-20000</v>
       </c>
       <c r="V96" s="3">
         <v>-20000</v>
       </c>
       <c r="W96" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-18000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-58000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-21000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-1000</v>
       </c>
       <c r="AE96" s="3">
         <v>-1000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1700</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-1900</v>
       </c>
       <c r="AL96" s="3">
         <v>-1900</v>
       </c>
       <c r="AM96" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9960,8 +10196,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10076,8 +10315,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10192,124 +10434,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-113000</v>
+      </c>
+      <c r="E100" s="3">
         <v>505000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>93000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-570000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-87000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>132000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-220000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1255000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-996000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1265000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-987000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-811000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-147000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-150000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>732000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-407000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-55000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>391000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-333000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-268000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>588000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1114000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-158000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>727000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>11000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>546000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-86000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-592000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-289000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-926000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-397000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-562400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>414200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>556600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-753400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>495400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>71300</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10346,8 +10594,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10424,120 +10672,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-45000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>311000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-504000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-31000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>365000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>58000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>201000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-432000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>525000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-183000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>72000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-104000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-143000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-391000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-493000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-88000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>595000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-534000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>373000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>77000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>211000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-160000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>96000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-106000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>449000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-505000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-251000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>255000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-422000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>240000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-251200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-600500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>269100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-612400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>398000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-1033000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VOYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
   <si>
     <t>VOYA</t>
   </si>
@@ -656,503 +656,515 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2031000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2111000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2128000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1981000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1969000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2010000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1956000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2033000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2051000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1819000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1823000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1871000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1835000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1538000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1345000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1524000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1506000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1677000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2009000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2503000</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X8" s="3">
+      <c r="X8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y8" s="3">
         <v>2231000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5505000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1719000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1705000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1844000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1878000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1972000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1848000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>837000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2259000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2114000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1981000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1281400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2185000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2192000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2059000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>8822000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2541200</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>884000</v>
+      </c>
+      <c r="E9" s="3">
         <v>939000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>915000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>859000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>897000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1043000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>993000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>899000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>907000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>861000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>856000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>739000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>810000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>83000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>60000</v>
-      </c>
-      <c r="R9" s="3">
-        <v>62000</v>
       </c>
       <c r="S9" s="3">
         <v>62000</v>
       </c>
       <c r="T9" s="3">
+        <v>62000</v>
+      </c>
+      <c r="U9" s="3">
         <v>40000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>190000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>26000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>539000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>16000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>336000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>19000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>76000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>46000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>36000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>43000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>57000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>-27000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>86000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>74000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>100000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>-34400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>209000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>195000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>64000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>415000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>180700</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1147000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1172000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1213000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1122000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1072000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>967000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>963000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1134000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1144000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>958000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>967000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1132000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1025000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1455000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1285000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1462000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1444000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1637000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1819000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2477000</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y10" s="3">
         <v>2215000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>5169000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1700000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1629000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1798000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1842000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1929000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1791000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>864000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2173000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2040000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1881000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1315800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1976000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1997000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1995000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>8407000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>2360500</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,8 +1206,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1313,8 +1326,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,8 +1448,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1461,83 +1480,83 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>70000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>12000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>80000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>15000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>10000</v>
-      </c>
-      <c r="T14" s="3">
-        <v>3000</v>
       </c>
       <c r="U14" s="3">
         <v>3000</v>
       </c>
       <c r="V14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="W14" s="3">
         <v>13000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>1000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>80000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>50000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>20000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>31000</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>3000</v>
       </c>
       <c r="AD14" s="3">
         <v>3000</v>
       </c>
       <c r="AE14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AF14" s="3">
         <v>26000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>6000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>7000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>14000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>15800</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>1000</v>
       </c>
       <c r="AL14" s="3">
         <v>1000</v>
@@ -1546,55 +1565,58 @@
         <v>1000</v>
       </c>
       <c r="AN14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AO14" s="3">
         <v>34000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E15" s="3">
         <v>27000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>26000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>25000</v>
       </c>
       <c r="G15" s="3">
         <v>25000</v>
       </c>
       <c r="H15" s="3">
+        <v>25000</v>
+      </c>
+      <c r="I15" s="3">
         <v>26000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>24000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>23000</v>
       </c>
       <c r="K15" s="3">
         <v>23000</v>
       </c>
       <c r="L15" s="3">
+        <v>23000</v>
+      </c>
+      <c r="M15" s="3">
         <v>22000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>21000</v>
       </c>
       <c r="N15" s="3">
         <v>21000</v>
       </c>
       <c r="O15" s="3">
+        <v>21000</v>
+      </c>
+      <c r="P15" s="3">
         <v>9000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1670,8 +1692,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,246 +1735,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1740000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1885000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1761000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1730000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1729000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1815000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1771000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1659000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1707000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1567000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1575000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1502000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1644000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1407000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1231000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1326000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1338000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1308000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1548000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1424000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-3049000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1682000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5510000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1711000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1618000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1716000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1670000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1671000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1699000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>667000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2018000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1811000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1905000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1000900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2078000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1965000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1883000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>8422000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>291000</v>
+      </c>
+      <c r="E18" s="3">
         <v>226000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>367000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>251000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>240000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>195000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>185000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>374000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>344000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>252000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>248000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>369000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>191000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>131000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>114000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>198000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>168000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>369000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>461000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1079000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y18" s="3">
         <v>549000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>8000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>87000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>128000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>208000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>301000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>149000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>170000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>241000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>303000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>76000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>280500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>107000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>227000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>176000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>400000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-283800</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1991,8 +2023,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2032,8 +2065,8 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -2053,11 +2086,11 @@
       <c r="V20" s="3">
         <v>0</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
@@ -2110,62 +2143,65 @@
       <c r="AO20" s="3">
         <v>0</v>
       </c>
+      <c r="AP20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>320000</v>
+      </c>
+      <c r="E21" s="3">
         <v>253000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>393000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>276000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>265000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>221000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>209000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>397000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>367000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>274000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>269000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>390000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>200000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>130000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T21" s="3">
         <v>179000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2175,15 +2211,15 @@
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="3">
         <v>549000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2229,365 +2265,377 @@
       <c r="AO21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E22" s="3">
         <v>57000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>60000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>63000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>67000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>75000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>69000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>98000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>57000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>80000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>76000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>94000</v>
-      </c>
-      <c r="O22" s="3">
-        <v>48000</v>
       </c>
       <c r="P22" s="3">
         <v>48000</v>
       </c>
       <c r="Q22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="R22" s="3">
         <v>43000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>46000</v>
       </c>
       <c r="S22" s="3">
         <v>46000</v>
       </c>
       <c r="T22" s="3">
+        <v>46000</v>
+      </c>
+      <c r="U22" s="3">
         <v>69000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>50000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>51000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>54000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>48000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>138000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>50000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>43000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>48000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>59000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>58000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>47000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>90000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>55000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>62000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>55000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>62300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>67000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>72000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>63000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>390000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>72100</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>230000</v>
+      </c>
+      <c r="E23" s="3">
         <v>169000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>307000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>188000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>173000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>120000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>116000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>276000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>287000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>102000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>172000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>263000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>141000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>83000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>71000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>152000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>122000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>300000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>411000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1028000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1038000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>501000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-143000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-42000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>44000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>80000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>149000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>243000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>102000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>80000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>186000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>241000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>218200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>40000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>155000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>113000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>10000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-355900</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E24" s="3">
         <v>20000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>35000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>27000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>22000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>18000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>41000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-17000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-74000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>28000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>12000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>29000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>9000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>11000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-202000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>40000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>112000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-48000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>55000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-72000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-264000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>33000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>9000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-41000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>21000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>45000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>42000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-40000</v>
       </c>
-      <c r="AL24" s="3">
-        <v>0</v>
-      </c>
       <c r="AM24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="3">
         <v>93000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-29000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-119400</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2705,246 +2753,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>195000</v>
+      </c>
+      <c r="E26" s="3">
         <v>149000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>272000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>161000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>151000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>121000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>98000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>235000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>288000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>119000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>246000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>235000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>129000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>137000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>42000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>143000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>111000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>502000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>371000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>916000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1086000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>446000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-71000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-48000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>50000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>344000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>144000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>210000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>93000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>121000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>165000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>196000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>17000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>176200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>80000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>155000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>20000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>39000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-236500</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E27" s="3">
         <v>136000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>176000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>162000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>139000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>93000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>98000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>201000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>234000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>118000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>248000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>154000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>69000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>190000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>166000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>64000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>54000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>398000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>143000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>465000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1072000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>318000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-136000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>27000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>30000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>334000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>111000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>184000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>84000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>57000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>142000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>138000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>17000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>94700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>15000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>103000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>19000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>10000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3062,8 +3119,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3116,73 +3176,76 @@
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>5000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-1000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-6000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>14000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-58000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-363000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-93000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-128000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-1119000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>42000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>64000</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>28000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>429000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-3259000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>134000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>64000</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>-162000</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-337000</v>
       </c>
-      <c r="AO29" s="3" t="s">
+      <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3363,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3419,8 +3485,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3460,8 +3529,8 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -3481,11 +3550,11 @@
       <c r="V32" s="3">
         <v>0</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y32" s="3">
         <v>0</v>
@@ -3538,127 +3607,133 @@
       <c r="AO32" s="3">
         <v>0</v>
       </c>
+      <c r="AP32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E33" s="3">
         <v>140000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>192000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>166000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>156000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>97000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>114000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>205000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>251000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>122000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>262000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>158000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>83000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>190000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>166000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>64000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>54000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>403000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>142000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>459000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1086000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>260000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-499000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-66000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-98000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-785000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>107000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>226000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>64000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>121000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>142000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>166000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>446000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>149000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>167000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-143000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-327000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3776,251 +3851,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E35" s="3">
         <v>140000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>192000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>166000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>156000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>97000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>114000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>205000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>251000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>122000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>262000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>158000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>83000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>190000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>166000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>64000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>54000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>403000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>142000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>459000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1086000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>260000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-499000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-66000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-98000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-785000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>107000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>226000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>64000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>121000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>142000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>166000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>446000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>149000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>167000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-143000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-327000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4062,8 +4146,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4105,169 +4190,173 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>969000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1228000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1157000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1179000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>868000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1399000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1457000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1066000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>995000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>937000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>829000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1195000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>724000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1007000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>935000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1039000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1125000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1573000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1818000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1850000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1316000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1723000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1136000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1149000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1085000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1249000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1450000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1541000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1340000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1568000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1885000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1620000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1597000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1435000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2072900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2713300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2531300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2229000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2951600</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>403000</v>
+      </c>
+      <c r="E42" s="3">
         <v>329000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>345000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>366000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>357000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>340000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>298000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>367000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>506000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>483000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>704000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>423000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>309000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4343,68 +4432,71 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>305000</v>
+      </c>
+      <c r="E43" s="3">
         <v>346000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>331000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>314000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>334000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>350000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>323000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>300000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>335000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>322000</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q43" s="3">
         <v>12426000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13561000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13079000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13261000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>13635000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>13580000</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>8</v>
       </c>
@@ -4417,8 +4509,8 @@
       <c r="Z43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
+      <c r="AA43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
@@ -4462,8 +4554,11 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4503,8 +4598,8 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4581,50 +4676,53 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12217000</v>
+      </c>
+      <c r="E45" s="3">
         <v>12284000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12417000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12556000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12809000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12917000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13298000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13160000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13476000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13647000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13296000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13899000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14330000</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -4700,50 +4798,53 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13894000</v>
+      </c>
+      <c r="E46" s="3">
         <v>14351000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14250000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14415000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14368000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15198000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15376000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14893000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15312000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15389000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14810000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15479000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15328000</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4819,127 +4920,133 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>27981000</v>
+      </c>
+      <c r="E47" s="3">
         <v>28518000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>28398000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>27906000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>27883000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>26015000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>26895000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>26353000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>26599000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>27352000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>27003000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>28304000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>29534000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>38086000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>38408000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>39911000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>41978000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>44387000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>47491000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>45341000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>44660000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>54841000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>54357000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>54264000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>51772000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>52700000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>67153000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>65417000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>64204000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>49918000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>62277000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>62241000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>63014000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>64644000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>93681000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>90575600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>89116700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>61153000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>93051100</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4979,8 +5086,8 @@
       <c r="O48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -5033,80 +5140,83 @@
       <c r="AG48" s="3">
         <v>0</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>8</v>
+      <c r="AH48" s="3">
+        <v>0</v>
       </c>
       <c r="AI48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AJ48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK48" s="3">
         <v>107000</v>
       </c>
-      <c r="AK48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AM48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AN48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO48" s="3">
         <v>112300</v>
       </c>
-      <c r="AO48" s="3" t="s">
+      <c r="AP48" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4032000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4079000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4076000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4115000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4163000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3728000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3783000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3800000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3831000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3855000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3926000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3858000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3884000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>958000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>824000</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>8</v>
       </c>
@@ -5122,8 +5232,8 @@
       <c r="W49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -5152,32 +5262,35 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>8</v>
+      <c r="AH49" s="3">
+        <v>0</v>
       </c>
       <c r="AI49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AJ49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK49" s="3">
         <v>186000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>196000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>197800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>208000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>219500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>227300</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5295,8 +5408,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5414,127 +5530,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>119665000</v>
+      </c>
+      <c r="E52" s="3">
         <v>124031000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>123132000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>118178000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>109583000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>111692000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>113757000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>108741000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>108270000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>102687000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>95386000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>99117000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>94652000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2223000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1931000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1795000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1405000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>986000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>691000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>690000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>935000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>21889000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>21494000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>21249000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>20902000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>22953000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>401000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>576000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>864000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>21655000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1122000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1266000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>58102000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>59833000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1663700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1756900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2055700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>66368800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1128100</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5652,127 +5774,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>173433000</v>
+      </c>
+      <c r="E54" s="3">
         <v>178859000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>177448000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>172436000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>163950000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>163889000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>166933000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>161280000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>161631000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>157085000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>149265000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>154616000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>151208000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>146606000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>144048000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>147520000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>161806000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>171262000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>168417000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>168194000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>162861000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>180518000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>171466000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>166934000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>155732000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>168990000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>166850000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>165162000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>161985000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>155430000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>165036000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>162740000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>219824000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>222532000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>226643900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>219838800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>217025500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>214585000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>218622200</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5814,8 +5942,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5857,8 +5986,9 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5898,8 +6028,8 @@
       <c r="O57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
+      <c r="P57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -5976,55 +6106,58 @@
       <c r="AO57" s="3">
         <v>0</v>
       </c>
+      <c r="AP57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2768000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2923000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2979000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2908000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2551000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2861000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1765000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1610000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1613000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1122000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1192000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1444000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1471000</v>
-      </c>
-      <c r="P58" s="3">
-        <v>141000</v>
       </c>
       <c r="Q58" s="3">
         <v>141000</v>
       </c>
       <c r="R58" s="3">
-        <v>1000</v>
+        <v>141000</v>
       </c>
       <c r="S58" s="3">
         <v>1000</v>
@@ -6060,10 +6193,10 @@
         <v>1000</v>
       </c>
       <c r="AD58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE58" s="3">
         <v>97000</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>1000</v>
       </c>
       <c r="AF58" s="3">
         <v>1000</v>
@@ -6075,28 +6208,31 @@
         <v>1000</v>
       </c>
       <c r="AI58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3">
         <v>337000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>336600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>735900</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>735500</v>
       </c>
-      <c r="AN58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AO58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6136,128 +6272,131 @@
       <c r="O59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q59" s="3">
         <v>81476000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>77358000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>81237000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>94232000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>101616000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>97995000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>98102000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>93872000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>90905000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>83454000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>80129000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>71002000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>83043000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>82049000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>81887000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>79627000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>71297000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>83034000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>80599000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>79668000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>79471000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>111603200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>105725300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>103261300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>67883100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>101627000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2768000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2923000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2979000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2908000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2551000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2861000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1765000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1610000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1613000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1122000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1192000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1444000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1471000</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6333,246 +6472,255 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2157000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1927000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1783000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1928000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2374000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2416000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2441000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2015000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2025000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2451000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2448000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2485000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2461000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>2094000</v>
       </c>
       <c r="Q61" s="3">
         <v>2094000</v>
       </c>
       <c r="R61" s="3">
+        <v>2094000</v>
+      </c>
+      <c r="S61" s="3">
         <v>2385000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2406000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2595000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2970000</v>
-      </c>
-      <c r="V61" s="3">
-        <v>2969000</v>
       </c>
       <c r="W61" s="3">
         <v>2969000</v>
       </c>
       <c r="X61" s="3">
+        <v>2969000</v>
+      </c>
+      <c r="Y61" s="3">
         <v>3044000</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>3043000</v>
       </c>
       <c r="Z61" s="3">
         <v>3043000</v>
       </c>
       <c r="AA61" s="3">
-        <v>3042000</v>
+        <v>3043000</v>
       </c>
       <c r="AB61" s="3">
         <v>3042000</v>
       </c>
       <c r="AC61" s="3">
-        <v>3041000</v>
+        <v>3042000</v>
       </c>
       <c r="AD61" s="3">
         <v>3041000</v>
       </c>
       <c r="AE61" s="3">
-        <v>3136000</v>
+        <v>3041000</v>
       </c>
       <c r="AF61" s="3">
         <v>3136000</v>
       </c>
       <c r="AG61" s="3">
+        <v>3136000</v>
+      </c>
+      <c r="AH61" s="3">
         <v>3459000</v>
-      </c>
-      <c r="AH61" s="3">
-        <v>3458000</v>
       </c>
       <c r="AI61" s="3">
         <v>3458000</v>
       </c>
       <c r="AJ61" s="3">
+        <v>3458000</v>
+      </c>
+      <c r="AK61" s="3">
         <v>3123000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3122200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2726200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2725700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3550000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3548500</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>161802000</v>
+      </c>
+      <c r="E62" s="3">
         <v>166636000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>165603000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>161047000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>152664000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>152274000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>156145000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>151786000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>152122000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>147109000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>140666000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>145159000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>141589000</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R62" s="3">
         <v>196000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>205000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>213000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>226000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>274000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>304000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>333000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>18976000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>18607000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>18465000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>18414000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>18966000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>409000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>445000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>465000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>18454000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>516000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>527000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>56998000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>58827000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>542200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>636800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>656000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>60250000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>631400</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,8 +6838,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6809,8 +6960,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6928,127 +7082,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>166727000</v>
+      </c>
+      <c r="E66" s="3">
         <v>171820000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>170365000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>165883000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>157589000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>157882000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>160351000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>155411000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>155760000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>151032000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>144306000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>149088000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>145521000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>143257000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>139955000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>143004000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>155608000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>163009000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>160028000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>159832000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>154930000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>170408000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>161809000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>157386000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>148305000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>159651000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>156299000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>155098000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>152920000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>147217000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>156513000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>154280000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>210446000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>212523000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>212990900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>206486600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>204135100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>201590000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>203416200</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7090,8 +7250,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7209,8 +7370,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7328,8 +7492,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7447,8 +7614,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7566,127 +7736,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1511000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1392000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1301000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1170000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1052000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>954000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>907000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>855000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>697000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>505000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>302000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>40000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-118000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-201000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-994000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1201000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1269000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1310000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-3238000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-3394000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-3857000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-4957000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5152000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-4833000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-4766000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-4718000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-11665000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-11785000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-12011000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-11732000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-11853000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-11995000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-12161000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-12719000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-9655600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-9804200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-9971400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-9742000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-9310300</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7804,8 +7980,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7923,8 +8102,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8042,127 +8224,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4658000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4953000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4957000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4629000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4383000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4005000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4719000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4043000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4153000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4193000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3127000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3697000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3954000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3349000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4093000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4516000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6198000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8253000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8389000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8362000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7931000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10110000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9657000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9548000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7427000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9339000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>10551000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>10064000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>9065000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8213000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8523000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8460000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>9378000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>10009000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>13653000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>13352200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>12890400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>12995000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>15206000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8280,251 +8468,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E81" s="3">
         <v>140000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>192000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>166000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>156000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>97000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>114000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>205000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>251000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>122000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>262000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>158000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>83000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>190000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>166000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>64000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>54000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>403000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>142000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>459000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1086000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>260000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-499000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-66000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-98000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-785000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>107000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>226000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>64000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>121000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>142000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>166000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>446000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-3164300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>149000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>167000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-143000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-327000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-248100</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8566,8 +8763,9 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8598,17 +8796,17 @@
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
         <v>-22000</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -8685,8 +8883,11 @@
       <c r="AO83" s="3">
         <v>0</v>
       </c>
+      <c r="AP83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8804,8 +9005,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8923,8 +9127,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9042,8 +9249,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9161,8 +9371,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9280,127 +9493,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E89" s="3">
         <v>557000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>168000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>742000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-179000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>79000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>719000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>316000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>231000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>364000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>403000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>715000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>156000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>219000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>418000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>296000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>419000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>140000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>121000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>747000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-936000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>421000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>788000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>508000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-76000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>459000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>302000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>418000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>131000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>234000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>580000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>653000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>401000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>456000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>570000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>605800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-49800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>3591000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>819700</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9442,8 +9661,9 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9483,8 +9703,8 @@
       <c r="O91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -9543,26 +9763,29 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK91" s="3">
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-9700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-10400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-66700</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-25800</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9680,8 +9903,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9799,127 +10025,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-352000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-372000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-718000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-524000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>245000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-23000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-486000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-92000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1082000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>833000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>430000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>797000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>472000</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-372000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-403000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-578000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-600000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>181000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>670000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-636000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1825000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-139000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-811000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-374000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-954000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>117000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-44000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-333000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-36000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-149000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>236000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-145000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1581300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-892500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>190800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-3683000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1924000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9961,127 +10193,131 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E96" s="3">
         <v>45000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>43000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>47000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>43000</v>
       </c>
       <c r="H96" s="3">
         <v>43000</v>
       </c>
       <c r="I96" s="3">
+        <v>43000</v>
+      </c>
+      <c r="J96" s="3">
         <v>44000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>43000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>41000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>42000</v>
       </c>
       <c r="M96" s="3">
         <v>42000</v>
       </c>
       <c r="N96" s="3">
+        <v>42000</v>
+      </c>
+      <c r="O96" s="3">
         <v>23000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>20000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-22000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-20000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-21000</v>
       </c>
       <c r="T96" s="3">
         <v>-21000</v>
       </c>
       <c r="U96" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-19000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-20000</v>
       </c>
       <c r="W96" s="3">
         <v>-20000</v>
       </c>
       <c r="X96" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-58000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-21000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-20000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-2000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-1000</v>
       </c>
       <c r="AF96" s="3">
         <v>-1000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-2500</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1700</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>-1900</v>
       </c>
       <c r="AM96" s="3">
         <v>-1900</v>
       </c>
       <c r="AN96" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-8000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10199,8 +10435,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10318,8 +10557,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10437,127 +10679,133 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-113000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>505000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>93000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-570000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-87000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>132000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-220000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1255000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-996000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1265000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-987000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-811000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-147000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-150000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>732000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-407000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-55000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>391000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-333000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-268000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>588000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1114000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-158000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>727000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>11000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>546000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-86000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-592000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-289000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-926000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-397000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-562400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>414200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>556600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-753400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>495400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>71300</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10597,8 +10845,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10675,123 +10923,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-258000</v>
+      </c>
+      <c r="E102" s="3">
         <v>72000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-45000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>311000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-504000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-31000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>365000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>58000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>201000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-432000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>525000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-183000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>72000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-104000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-143000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-391000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-493000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-88000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>595000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-534000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>373000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>77000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>211000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-160000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>96000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-106000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>449000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-505000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-251000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>255000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-422000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>240000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-251200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-600500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>269100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-612400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>398000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-1033000</v>
       </c>
     </row>
